--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -50,7 +50,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,8 +69,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -111,11 +116,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -160,6 +179,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -234,6 +283,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>레어도 (전역 등급)</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>기본 가격 (즉시 판매·거래소 하한의 기준)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -532,7 +601,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -540,10 +609,14 @@
   <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
-    <col width="12.33203125" customWidth="1" style="15" min="1" max="1"/>
-    <col width="13.6640625" customWidth="1" style="15" min="4" max="5"/>
-    <col width="16.33203125" customWidth="1" style="15" min="6" max="6"/>
-    <col width="16.33203125" customWidth="1" style="15" min="7" max="7"/>
+    <col width="15" customWidth="1" style="15" min="1" max="1"/>
+    <col width="12" customWidth="1" style="15" min="2" max="2"/>
+    <col width="19" customWidth="1" style="15" min="3" max="3"/>
+    <col width="13" customWidth="1" style="15" min="4" max="5"/>
+    <col width="15" customWidth="1" style="15" min="5" max="5"/>
+    <col width="11" customWidth="1" style="15" min="6" max="6"/>
+    <col width="11" customWidth="1" style="15" min="7" max="7"/>
+    <col width="19" customWidth="1" style="15" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -553,39 +626,39 @@
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>아이템 TID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="18" t="inlineStr">
         <is>
           <t>아이템 타입</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>레어도 (전역 등급)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>레어도</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
         <is>
           <t>최대 수량</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>기본 가격 (즉시 판매·거래소 하한의 기준)</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>기본 가격</t>
+        </is>
+      </c>
+      <c r="H2" s="18" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
@@ -595,37 +668,37 @@
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -637,37 +710,37 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>eItemType</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>eGlobalRarity</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -679,15 +752,15 @@
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n">
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="3" t="n"/>
+      <c r="H5" s="20" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -695,13 +768,13 @@
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -709,13 +782,13 @@
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -723,37 +796,37 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>ItemTID</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>ItemType</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>GlobalRarity</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>MaxStack</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>BasePrice</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -761,7 +834,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="11" t="n">
         <v>10001</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -769,12 +842,12 @@
           <t>붕어</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
@@ -793,7 +866,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n"/>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="11" t="n">
         <v>10002</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -801,12 +874,12 @@
           <t>잉어</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -825,7 +898,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="11" t="n">
         <v>10003</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -833,12 +906,12 @@
           <t>월척 붕어</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
@@ -857,7 +930,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n"/>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="11" t="n">
         <v>10004</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -865,12 +938,12 @@
           <t>향어</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
@@ -889,7 +962,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="11" t="n">
         <v>10005</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -897,12 +970,12 @@
           <t>대물 잉어</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
@@ -921,7 +994,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n"/>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="11" t="n">
         <v>10006</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -929,12 +1002,12 @@
           <t>전설의 잉어</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
@@ -953,20 +1026,20 @@
     </row>
     <row r="15" ht="16.5" customHeight="1" s="15">
       <c r="A15" s="4" t="n"/>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="11" t="n">
         <v>20001</v>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>밀</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
@@ -977,7 +1050,7 @@
       <c r="G15" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>텃밭(Lv1)</t>
         </is>
@@ -985,20 +1058,20 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="11" t="n">
         <v>20002</v>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>감자</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
@@ -1009,7 +1082,7 @@
       <c r="G16" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>텃밭(Lv1)</t>
         </is>
@@ -1017,20 +1090,20 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="11" t="n">
         <v>20003</v>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>옥수수</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
@@ -1041,7 +1114,7 @@
       <c r="G17" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>텃밭(Lv1)</t>
         </is>
@@ -1049,20 +1122,20 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="11" t="n">
         <v>20004</v>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>인삼</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
@@ -1073,7 +1146,7 @@
       <c r="G18" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>텃밭(Lv1)</t>
         </is>
@@ -1081,20 +1154,20 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="11" t="n">
         <v>20005</v>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>변종 인삼</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
@@ -1105,7 +1178,7 @@
       <c r="G19" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>텃밭(Lv1)</t>
         </is>
@@ -1113,20 +1186,20 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="11" t="n">
         <v>20006</v>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>태초의 씨앗</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
@@ -1137,7 +1210,7 @@
       <c r="G20" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>텃밭(Lv1)</t>
         </is>
@@ -1145,31 +1218,31 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="11" t="n">
         <v>30001</v>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>잡목</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G21" s="7" t="n">
+      <c r="F21" s="11" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G21" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>잡목림(Lv1)</t>
         </is>
@@ -1177,31 +1250,31 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="11" t="n">
         <v>30002</v>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>소나무 목재</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F22" s="7" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G22" s="7" t="n">
+      <c r="F22" s="11" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G22" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>잡목림(Lv1)</t>
         </is>
@@ -1209,31 +1282,31 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="11" t="n">
         <v>30003</v>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>참나무 목재</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F23" s="7" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G23" s="7" t="n">
+      <c r="F23" s="11" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G23" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>잡목림(Lv1)</t>
         </is>
@@ -1241,31 +1314,31 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="11" t="n">
         <v>30004</v>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>흑단 목재</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F24" s="7" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G24" s="7" t="n">
+      <c r="F24" s="11" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G24" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>잡목림(Lv1)</t>
         </is>
@@ -1273,31 +1346,31 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="11" t="n">
         <v>30005</v>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>고급 원목</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F25" s="7" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G25" s="7" t="n">
+      <c r="F25" s="11" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G25" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>잡목림(Lv1)</t>
         </is>
@@ -1305,31 +1378,31 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="11" t="n">
         <v>30006</v>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>세계수 가지</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F26" s="7" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G26" s="7" t="n">
+      <c r="F26" s="11" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G26" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>잡목림(Lv1)</t>
         </is>
@@ -1337,31 +1410,31 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="11" t="n">
         <v>40001</v>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>돌덩어리</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F27" s="7" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G27" s="7" t="n">
+      <c r="F27" s="11" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G27" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>노천 광산(Lv1)</t>
         </is>
@@ -1369,4247 +1442,4247 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="11" t="n">
         <v>40002</v>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>구리 광석</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F28" s="7" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G28" s="7" t="n">
+      <c r="F28" s="11" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G28" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>노천 광산(Lv1)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="23" t="n">
         <v>40003</v>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>은광석</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F29" s="13" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G29" s="13" t="n">
+      <c r="F29" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G29" s="23" t="n">
         <v>60</v>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H29" s="24" t="inlineStr">
         <is>
           <t>노천 광산(Lv1)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="25" t="n">
         <v>40004</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>금광석</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="F30" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G30" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>노천 광산(Lv1)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="25" t="n">
         <v>40005</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>보석 원석</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="F31" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G31" s="25" t="n">
         <v>400</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>노천 광산(Lv1)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="25" t="n">
         <v>40006</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>심연의 원석</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G32" t="n">
+      <c r="F32" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G32" s="25" t="n">
         <v>1000</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>노천 광산(Lv1)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="25" t="n">
         <v>50001</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>질긴 고기</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G33" t="n">
+      <c r="F33" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G33" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>들판(Lv1)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="14" t="n">
+      <c r="B34" s="25" t="n">
         <v>50002</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>토끼 가죽</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="F34" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G34" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>들판(Lv1)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="14" t="n">
+      <c r="B35" s="25" t="n">
         <v>50003</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>늑대 가죽</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="F35" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G35" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>들판(Lv1)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="14" t="n">
+      <c r="B36" s="25" t="n">
         <v>50004</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>곰 모피</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="F36" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G36" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>들판(Lv1)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="14" t="n">
+      <c r="B37" s="25" t="n">
         <v>50005</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>거대한 뿔</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="F37" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G37" s="25" t="n">
         <v>400</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>들판(Lv1)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="14" t="n">
+      <c r="B38" s="25" t="n">
         <v>50006</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>마수의 심장</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="F38" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G38" s="25" t="n">
         <v>1000</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>들판(Lv1)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="14" t="n">
+      <c r="B39" s="25" t="n">
         <v>10011</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>피라미</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="F39" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G39" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>저수지(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="14" t="n">
+      <c r="B40" s="25" t="n">
         <v>10012</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>메기</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="F40" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G40" s="25" t="n">
         <v>75</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>저수지(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="14" t="n">
+      <c r="B41" s="25" t="n">
         <v>10013</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>가물치</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="F41" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G41" s="25" t="n">
         <v>180</v>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>저수지(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="14" t="n">
+      <c r="B42" s="25" t="n">
         <v>10014</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>백년 메기</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G42" t="n">
+      <c r="F42" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G42" s="25" t="n">
         <v>450</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>저수지(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="14" t="n">
+      <c r="B43" s="25" t="n">
         <v>10015</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>저수지의 주인</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="F43" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G43" s="25" t="n">
         <v>1200</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>저수지(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="14" t="n">
+      <c r="B44" s="25" t="n">
         <v>10016</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>용왕의 사자</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G44" t="n">
+      <c r="F44" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G44" s="25" t="n">
         <v>3000</v>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>저수지(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="14" t="n">
+      <c r="B45" s="25" t="n">
         <v>10021</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>모래무지</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G45" t="n">
+      <c r="F45" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G45" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>강 하류(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="14" t="n">
+      <c r="B46" s="25" t="n">
         <v>10022</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>쏘가리</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G46" t="n">
+      <c r="F46" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G46" s="25" t="n">
         <v>225</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>강 하류(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="14" t="n">
+      <c r="B47" s="25" t="n">
         <v>10023</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>황금 잉어</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G47" t="n">
+      <c r="F47" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G47" s="25" t="n">
         <v>540</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>강 하류(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="14" t="n">
+      <c r="B48" s="25" t="n">
         <v>10024</v>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>강의 수호자</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G48" t="n">
+      <c r="F48" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G48" s="25" t="n">
         <v>1350</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>강 하류(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="14" t="n">
+      <c r="B49" s="25" t="n">
         <v>10025</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>천년 쏘가리</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G49" t="n">
+      <c r="F49" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G49" s="25" t="n">
         <v>3600</v>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>강 하류(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="14" t="n">
+      <c r="B50" s="25" t="n">
         <v>10026</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>강신의 비늘</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G50" t="n">
+      <c r="F50" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G50" s="25" t="n">
         <v>9000</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>강 하류(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="14" t="n">
+      <c r="B51" s="25" t="n">
         <v>10031</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>빙어</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G51" t="n">
+      <c r="F51" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G51" s="25" t="n">
         <v>270</v>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>호수(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="14" t="n">
+      <c r="B52" s="25" t="n">
         <v>10032</v>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>송어</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G52" t="n">
+      <c r="F52" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G52" s="25" t="n">
         <v>675</v>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>호수(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="14" t="n">
+      <c r="B53" s="25" t="n">
         <v>10033</v>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>무지개 송어</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G53" t="n">
+      <c r="F53" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G53" s="25" t="n">
         <v>1620</v>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>호수(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="14" t="n">
+      <c r="B54" s="25" t="n">
         <v>10034</v>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>호수의 눈</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="F54" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G54" s="25" t="n">
         <v>4050</v>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>호수(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="14" t="n">
+      <c r="B55" s="25" t="n">
         <v>10035</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>심층 대어</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G55" t="n">
+      <c r="F55" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G55" s="25" t="n">
         <v>10800</v>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="4" t="inlineStr">
         <is>
           <t>호수(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="14" t="n">
+      <c r="B56" s="25" t="n">
         <v>10036</v>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>호수의 심장</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G56" t="n">
+      <c r="F56" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G56" s="25" t="n">
         <v>27000</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>호수(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="14" t="n">
+      <c r="B57" s="25" t="n">
         <v>10041</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>심해 새우</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G57" t="n">
+      <c r="F57" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G57" s="25" t="n">
         <v>810</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>심해(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="14" t="n">
+      <c r="B58" s="25" t="n">
         <v>10042</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>아귀</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="F58" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G58" s="25" t="n">
         <v>2025</v>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>심해(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="14" t="n">
+      <c r="B59" s="25" t="n">
         <v>10043</v>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>심해 등불고기</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G59" t="n">
+      <c r="F59" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G59" s="25" t="n">
         <v>4860</v>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="4" t="inlineStr">
         <is>
           <t>심해(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="14" t="n">
+      <c r="B60" s="25" t="n">
         <v>10044</v>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>대왕오징어</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G60" t="n">
+      <c r="F60" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G60" s="25" t="n">
         <v>12150</v>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>심해(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="14" t="n">
+      <c r="B61" s="25" t="n">
         <v>10045</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>해구의 지배자</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G61" t="n">
+      <c r="F61" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G61" s="25" t="n">
         <v>32400</v>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>심해(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="14" t="n">
+      <c r="B62" s="25" t="n">
         <v>10046</v>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>리바이어던의 조각</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G62" t="n">
+      <c r="F62" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G62" s="25" t="n">
         <v>81000</v>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="4" t="inlineStr">
         <is>
           <t>심해(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="14" t="n">
+      <c r="B63" s="25" t="n">
         <v>20011</v>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>보리</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G63" t="n">
+      <c r="F63" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G63" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>밭(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="14" t="n">
+      <c r="B64" s="25" t="n">
         <v>20012</v>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>고구마</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G64" t="n">
+      <c r="F64" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G64" s="25" t="n">
         <v>75</v>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>밭(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="14" t="n">
+      <c r="B65" s="25" t="n">
         <v>20013</v>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>호박</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G65" t="n">
+      <c r="F65" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G65" s="25" t="n">
         <v>180</v>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="4" t="inlineStr">
         <is>
           <t>밭(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="14" t="n">
+      <c r="B66" s="25" t="n">
         <v>20014</v>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>백년초</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G66" t="n">
+      <c r="F66" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G66" s="25" t="n">
         <v>450</v>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="4" t="inlineStr">
         <is>
           <t>밭(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="14" t="n">
+      <c r="B67" s="25" t="n">
         <v>20015</v>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>황금 호박</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G67" t="n">
+      <c r="F67" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G67" s="25" t="n">
         <v>1200</v>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>밭(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="14" t="n">
+      <c r="B68" s="25" t="n">
         <v>20016</v>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>불멸의 뿌리</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F68" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G68" t="n">
+      <c r="F68" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G68" s="25" t="n">
         <v>3000</v>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
         <is>
           <t>밭(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="14" t="n">
+      <c r="B69" s="25" t="n">
         <v>20021</v>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>벼</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G69" t="n">
+      <c r="F69" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G69" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="4" t="inlineStr">
         <is>
           <t>농장(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="14" t="n">
+      <c r="B70" s="25" t="n">
         <v>20022</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>콩</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G70" t="n">
+      <c r="F70" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G70" s="25" t="n">
         <v>225</v>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>농장(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="14" t="n">
+      <c r="B71" s="25" t="n">
         <v>20023</v>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>딸기</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G71" t="n">
+      <c r="F71" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G71" s="25" t="n">
         <v>540</v>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" s="4" t="inlineStr">
         <is>
           <t>농장(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="14" t="n">
+      <c r="B72" s="25" t="n">
         <v>20024</v>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>산삼</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G72" t="n">
+      <c r="F72" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G72" s="25" t="n">
         <v>1350</v>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72" s="4" t="inlineStr">
         <is>
           <t>농장(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="14" t="n">
+      <c r="B73" s="25" t="n">
         <v>20025</v>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>천년 산삼</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G73" t="n">
+      <c r="F73" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G73" s="25" t="n">
         <v>3600</v>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="4" t="inlineStr">
         <is>
           <t>농장(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="14" t="n">
+      <c r="B74" s="25" t="n">
         <v>20026</v>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>생명의 열매</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F74" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G74" t="n">
+      <c r="F74" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G74" s="25" t="n">
         <v>9000</v>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>농장(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="14" t="n">
+      <c r="B75" s="25" t="n">
         <v>20031</v>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>목화</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G75" t="n">
+      <c r="F75" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G75" s="25" t="n">
         <v>270</v>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>대농장(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="14" t="n">
+      <c r="B76" s="25" t="n">
         <v>20032</v>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>사탕수수</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G76" t="n">
+      <c r="F76" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G76" s="25" t="n">
         <v>675</v>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>대농장(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="14" t="n">
+      <c r="B77" s="25" t="n">
         <v>20033</v>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>커피 열매</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G77" t="n">
+      <c r="F77" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G77" s="25" t="n">
         <v>1620</v>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H77" s="4" t="inlineStr">
         <is>
           <t>대농장(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="14" t="n">
+      <c r="B78" s="25" t="n">
         <v>20034</v>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>흑진주 포도</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G78" t="n">
+      <c r="F78" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G78" s="25" t="n">
         <v>4050</v>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>대농장(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="14" t="n">
+      <c r="B79" s="25" t="n">
         <v>20035</v>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>무지개 밀</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G79" t="n">
+      <c r="F79" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G79" s="25" t="n">
         <v>10800</v>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H79" s="4" t="inlineStr">
         <is>
           <t>대농장(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="14" t="n">
+      <c r="B80" s="25" t="n">
         <v>20036</v>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>세계수의 씨앗</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F80" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G80" t="n">
+      <c r="F80" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G80" s="25" t="n">
         <v>27000</v>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>대농장(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="14" t="n">
+      <c r="B81" s="25" t="n">
         <v>20041</v>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>정화된 흙</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F81" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G81" t="n">
+      <c r="F81" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G81" s="25" t="n">
         <v>810</v>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81" s="4" t="inlineStr">
         <is>
           <t>신성한 대지(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="14" t="n">
+      <c r="B82" s="25" t="n">
         <v>20042</v>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>성스러운 이삭</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F82" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G82" t="n">
+      <c r="F82" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G82" s="25" t="n">
         <v>2025</v>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>신성한 대지(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="14" t="n">
+      <c r="B83" s="25" t="n">
         <v>20043</v>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>영약초</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F83" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G83" t="n">
+      <c r="F83" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G83" s="25" t="n">
         <v>4860</v>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H83" s="4" t="inlineStr">
         <is>
           <t>신성한 대지(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="14" t="n">
+      <c r="B84" s="25" t="n">
         <v>20044</v>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>신월초</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F84" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G84" t="n">
+      <c r="F84" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G84" s="25" t="n">
         <v>12150</v>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>신성한 대지(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="14" t="n">
+      <c r="B85" s="25" t="n">
         <v>20045</v>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>신들의 곡식</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F85" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G85" t="n">
+      <c r="F85" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G85" s="25" t="n">
         <v>32400</v>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H85" s="4" t="inlineStr">
         <is>
           <t>신성한 대지(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="14" t="n">
+      <c r="B86" s="25" t="n">
         <v>20046</v>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>창세의 열매</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F86" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G86" t="n">
+      <c r="F86" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G86" s="25" t="n">
         <v>81000</v>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H86" s="4" t="inlineStr">
         <is>
           <t>신성한 대지(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="14" t="n">
+      <c r="B87" s="25" t="n">
         <v>30011</v>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>잔가지</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F87" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G87" t="n">
+      <c r="F87" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G87" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H87" s="4" t="inlineStr">
         <is>
           <t>소나무 숲(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="14" t="n">
+      <c r="B88" s="25" t="n">
         <v>30012</v>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>삼나무 목재</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F88" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G88" t="n">
+      <c r="F88" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G88" s="25" t="n">
         <v>75</v>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H88" s="4" t="inlineStr">
         <is>
           <t>소나무 숲(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="14" t="n">
+      <c r="B89" s="25" t="n">
         <v>30013</v>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>편백나무 목재</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F89" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G89" t="n">
+      <c r="F89" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G89" s="25" t="n">
         <v>180</v>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H89" s="4" t="inlineStr">
         <is>
           <t>소나무 숲(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="14" t="n">
+      <c r="B90" s="25" t="n">
         <v>30014</v>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>홍송 원목</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F90" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G90" t="n">
+      <c r="F90" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G90" s="25" t="n">
         <v>450</v>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H90" s="4" t="inlineStr">
         <is>
           <t>소나무 숲(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="14" t="n">
+      <c r="B91" s="25" t="n">
         <v>30015</v>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>천년 소나무</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G91" t="n">
+      <c r="F91" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G91" s="25" t="n">
         <v>1200</v>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H91" s="4" t="inlineStr">
         <is>
           <t>소나무 숲(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="14" t="n">
+      <c r="B92" s="25" t="n">
         <v>30016</v>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>숲의 정령목</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F92" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G92" t="n">
+      <c r="F92" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G92" s="25" t="n">
         <v>3000</v>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t>소나무 숲(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="14" t="n">
+      <c r="B93" s="25" t="n">
         <v>30021</v>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>도토리 가지</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G93" t="n">
+      <c r="F93" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G93" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H93" s="4" t="inlineStr">
         <is>
           <t>참나무 숲(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="14" t="n">
+      <c r="B94" s="25" t="n">
         <v>30022</v>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>너도밤나무 목재</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F94" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G94" t="n">
+      <c r="F94" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G94" s="25" t="n">
         <v>225</v>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H94" s="4" t="inlineStr">
         <is>
           <t>참나무 숲(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="14" t="n">
+      <c r="B95" s="25" t="n">
         <v>30023</v>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>단풍나무 목재</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F95" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G95" t="n">
+      <c r="F95" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G95" s="25" t="n">
         <v>540</v>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H95" s="4" t="inlineStr">
         <is>
           <t>참나무 숲(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="14" t="n">
+      <c r="B96" s="25" t="n">
         <v>30024</v>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>고목의 심재</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F96" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G96" t="n">
+      <c r="F96" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G96" s="25" t="n">
         <v>1350</v>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H96" s="4" t="inlineStr">
         <is>
           <t>참나무 숲(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="14" t="n">
+      <c r="B97" s="25" t="n">
         <v>30025</v>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>백년 참나무</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F97" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G97" t="n">
+      <c r="F97" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G97" s="25" t="n">
         <v>3600</v>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H97" s="4" t="inlineStr">
         <is>
           <t>참나무 숲(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="14" t="n">
+      <c r="B98" s="25" t="n">
         <v>30026</v>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>대지의 뿌리</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F98" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G98" t="n">
+      <c r="F98" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G98" s="25" t="n">
         <v>9000</v>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H98" s="4" t="inlineStr">
         <is>
           <t>참나무 숲(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="14" t="n">
+      <c r="B99" s="25" t="n">
         <v>30031</v>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>그을린 통나무</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E99" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F99" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G99" t="n">
+      <c r="F99" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G99" s="25" t="n">
         <v>270</v>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H99" s="4" t="inlineStr">
         <is>
           <t>흑림(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="14" t="n">
+      <c r="B100" s="25" t="n">
         <v>30032</v>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>흑참나무 목재</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E100" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F100" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G100" t="n">
+      <c r="F100" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G100" s="25" t="n">
         <v>675</v>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H100" s="4" t="inlineStr">
         <is>
           <t>흑림(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="14" t="n">
+      <c r="B101" s="25" t="n">
         <v>30033</v>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>자단 목재</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F101" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G101" t="n">
+      <c r="F101" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G101" s="25" t="n">
         <v>1620</v>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H101" s="4" t="inlineStr">
         <is>
           <t>흑림(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="14" t="n">
+      <c r="B102" s="25" t="n">
         <v>30034</v>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>마력 깃든 목재</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F102" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G102" t="n">
+      <c r="F102" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G102" s="25" t="n">
         <v>4050</v>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H102" s="4" t="inlineStr">
         <is>
           <t>흑림(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="14" t="n">
+      <c r="B103" s="25" t="n">
         <v>30035</v>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>흑림의 고목</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F103" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G103" t="n">
+      <c r="F103" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G103" s="25" t="n">
         <v>10800</v>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H103" s="4" t="inlineStr">
         <is>
           <t>흑림(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="14" t="n">
+      <c r="B104" s="25" t="n">
         <v>30036</v>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>어둠나무의 핵</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E104" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F104" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G104" t="n">
+      <c r="F104" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G104" s="25" t="n">
         <v>27000</v>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H104" s="4" t="inlineStr">
         <is>
           <t>흑림(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="14" t="n">
+      <c r="B105" s="25" t="n">
         <v>30041</v>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>세계수 껍질</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F105" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G105" t="n">
+      <c r="F105" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G105" s="25" t="n">
         <v>810</v>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H105" s="4" t="inlineStr">
         <is>
           <t>세계수 뿌리(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="14" t="n">
+      <c r="B106" s="25" t="n">
         <v>30042</v>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>빛나는 수액</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E106" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F106" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G106" t="n">
+      <c r="F106" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G106" s="25" t="n">
         <v>2025</v>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H106" s="4" t="inlineStr">
         <is>
           <t>세계수 뿌리(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="14" t="n">
+      <c r="B107" s="25" t="n">
         <v>30043</v>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>신목 목재</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E107" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F107" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G107" t="n">
+      <c r="F107" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G107" s="25" t="n">
         <v>4860</v>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="H107" s="4" t="inlineStr">
         <is>
           <t>세계수 뿌리(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="14" t="n">
+      <c r="B108" s="25" t="n">
         <v>30044</v>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="4" t="inlineStr">
         <is>
           <t>영원의 나이테</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E108" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F108" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G108" t="n">
+      <c r="F108" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G108" s="25" t="n">
         <v>12150</v>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="H108" s="4" t="inlineStr">
         <is>
           <t>세계수 뿌리(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="14" t="n">
+      <c r="B109" s="25" t="n">
         <v>30045</v>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>세계수 심재</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D109" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F109" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G109" t="n">
+      <c r="F109" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G109" s="25" t="n">
         <v>32400</v>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="H109" s="4" t="inlineStr">
         <is>
           <t>세계수 뿌리(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="14" t="n">
+      <c r="B110" s="25" t="n">
         <v>30046</v>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>창세목의 조각</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D110" s="4" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E110" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F110" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G110" t="n">
+      <c r="F110" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G110" s="25" t="n">
         <v>81000</v>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H110" s="4" t="inlineStr">
         <is>
           <t>세계수 뿌리(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="B111" s="14" t="n">
+      <c r="B111" s="25" t="n">
         <v>40011</v>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="4" t="inlineStr">
         <is>
           <t>석회암</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D111" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E111" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F111" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G111" t="n">
+      <c r="F111" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G111" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="H111" s="4" t="inlineStr">
         <is>
           <t>갱도(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="B112" s="14" t="n">
+      <c r="B112" s="25" t="n">
         <v>40012</v>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>주석 광석</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E112" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F112" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G112" t="n">
+      <c r="F112" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G112" s="25" t="n">
         <v>75</v>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="H112" s="4" t="inlineStr">
         <is>
           <t>갱도(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="14" t="n">
+      <c r="B113" s="25" t="n">
         <v>40013</v>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>철광석</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F113" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G113" t="n">
+      <c r="F113" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G113" s="25" t="n">
         <v>180</v>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="H113" s="4" t="inlineStr">
         <is>
           <t>갱도(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="B114" s="14" t="n">
+      <c r="B114" s="25" t="n">
         <v>40014</v>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>백금 광석</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E114" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F114" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G114" t="n">
+      <c r="F114" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G114" s="25" t="n">
         <v>450</v>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="H114" s="4" t="inlineStr">
         <is>
           <t>갱도(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="B115" s="14" t="n">
+      <c r="B115" s="25" t="n">
         <v>40015</v>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr">
         <is>
           <t>청옥 원석</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E115" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F115" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G115" t="n">
+      <c r="F115" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G115" s="25" t="n">
         <v>1200</v>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="H115" s="4" t="inlineStr">
         <is>
           <t>갱도(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="B116" s="14" t="n">
+      <c r="B116" s="25" t="n">
         <v>40016</v>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="4" t="inlineStr">
         <is>
           <t>지맥의 결정</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="E116" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F116" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G116" t="n">
+      <c r="F116" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G116" s="25" t="n">
         <v>3000</v>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="H116" s="4" t="inlineStr">
         <is>
           <t>갱도(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="B117" s="14" t="n">
+      <c r="B117" s="25" t="n">
         <v>40021</v>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>현무암</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F117" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G117" t="n">
+      <c r="F117" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G117" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H117" s="4" t="inlineStr">
         <is>
           <t>심층 갱도(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="B118" s="14" t="n">
+      <c r="B118" s="25" t="n">
         <v>40022</v>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>아연 광석</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E118" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F118" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G118" t="n">
+      <c r="F118" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G118" s="25" t="n">
         <v>225</v>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="H118" s="4" t="inlineStr">
         <is>
           <t>심층 갱도(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="B119" s="14" t="n">
+      <c r="B119" s="25" t="n">
         <v>40023</v>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>미스릴 광석</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E119" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F119" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G119" t="n">
+      <c r="F119" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G119" s="25" t="n">
         <v>540</v>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="H119" s="4" t="inlineStr">
         <is>
           <t>심층 갱도(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="B120" s="14" t="n">
+      <c r="B120" s="25" t="n">
         <v>40024</v>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>홍옥 원석</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E120" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F120" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G120" t="n">
+      <c r="F120" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G120" s="25" t="n">
         <v>1350</v>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="H120" s="4" t="inlineStr">
         <is>
           <t>심층 갱도(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="B121" s="14" t="n">
+      <c r="B121" s="25" t="n">
         <v>40025</v>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>흑요석 결정</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E121" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F121" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G121" t="n">
+      <c r="F121" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G121" s="25" t="n">
         <v>3600</v>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="H121" s="4" t="inlineStr">
         <is>
           <t>심층 갱도(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="B122" s="14" t="n">
+      <c r="B122" s="25" t="n">
         <v>40026</v>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>대지의 핵</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E122" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F122" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G122" t="n">
+      <c r="F122" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G122" s="25" t="n">
         <v>9000</v>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H122" s="4" t="inlineStr">
         <is>
           <t>심층 갱도(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="B123" s="14" t="n">
+      <c r="B123" s="25" t="n">
         <v>40031</v>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>수정 파편</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E123" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F123" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G123" t="n">
+      <c r="F123" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G123" s="25" t="n">
         <v>270</v>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H123" s="4" t="inlineStr">
         <is>
           <t>지하 대공동(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="B124" s="14" t="n">
+      <c r="B124" s="25" t="n">
         <v>40032</v>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>코발트 광석</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D124" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E124" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F124" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G124" t="n">
+      <c r="F124" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G124" s="25" t="n">
         <v>675</v>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="H124" s="4" t="inlineStr">
         <is>
           <t>지하 대공동(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="B125" s="14" t="n">
+      <c r="B125" s="25" t="n">
         <v>40033</v>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr">
         <is>
           <t>오리하르콘 광석</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E125" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F125" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G125" t="n">
+      <c r="F125" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G125" s="25" t="n">
         <v>1620</v>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H125" s="4" t="inlineStr">
         <is>
           <t>지하 대공동(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="B126" s="14" t="n">
+      <c r="B126" s="25" t="n">
         <v>40034</v>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="4" t="inlineStr">
         <is>
           <t>자수정 원석</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E126" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F126" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G126" t="n">
+      <c r="F126" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G126" s="25" t="n">
         <v>4050</v>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="H126" s="4" t="inlineStr">
         <is>
           <t>지하 대공동(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="B127" s="14" t="n">
+      <c r="B127" s="25" t="n">
         <v>40035</v>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="4" t="inlineStr">
         <is>
           <t>별빛 광석</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E127" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F127" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G127" t="n">
+      <c r="F127" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G127" s="25" t="n">
         <v>10800</v>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="H127" s="4" t="inlineStr">
         <is>
           <t>지하 대공동(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="B128" s="14" t="n">
+      <c r="B128" s="25" t="n">
         <v>40036</v>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="4" t="inlineStr">
         <is>
           <t>공동의 심장</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E128" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F128" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G128" t="n">
+      <c r="F128" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G128" s="25" t="n">
         <v>27000</v>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H128" s="4" t="inlineStr">
         <is>
           <t>지하 대공동(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="B129" s="14" t="n">
+      <c r="B129" s="25" t="n">
         <v>40041</v>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="4" t="inlineStr">
         <is>
           <t>심연의 파편</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E129" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F129" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G129" t="n">
+      <c r="F129" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G129" s="25" t="n">
         <v>810</v>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H129" s="4" t="inlineStr">
         <is>
           <t>심연(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="B130" s="14" t="n">
+      <c r="B130" s="25" t="n">
         <v>40042</v>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr">
         <is>
           <t>암흑 광석</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F130" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G130" t="n">
+      <c r="F130" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G130" s="25" t="n">
         <v>2025</v>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H130" s="4" t="inlineStr">
         <is>
           <t>심연(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="B131" s="14" t="n">
+      <c r="B131" s="25" t="n">
         <v>40043</v>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>아다만트 광석</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F131" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G131" t="n">
+      <c r="F131" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G131" s="25" t="n">
         <v>4860</v>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H131" s="4" t="inlineStr">
         <is>
           <t>심연(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="B132" s="14" t="n">
+      <c r="B132" s="25" t="n">
         <v>40044</v>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C132" s="4" t="inlineStr">
         <is>
           <t>심연의 수정</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E132" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F132" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G132" t="n">
+      <c r="F132" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G132" s="25" t="n">
         <v>12150</v>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="H132" s="4" t="inlineStr">
         <is>
           <t>심연(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="B133" s="14" t="n">
+      <c r="B133" s="25" t="n">
         <v>40045</v>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C133" s="4" t="inlineStr">
         <is>
           <t>용해된 별의 조각</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E133" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F133" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G133" t="n">
+      <c r="F133" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G133" s="25" t="n">
         <v>32400</v>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H133" s="4" t="inlineStr">
         <is>
           <t>심연(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="B134" s="14" t="n">
+      <c r="B134" s="25" t="n">
         <v>40046</v>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C134" s="4" t="inlineStr">
         <is>
           <t>세계의 축</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" s="4" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E134" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F134" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G134" t="n">
+      <c r="F134" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G134" s="25" t="n">
         <v>81000</v>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H134" s="4" t="inlineStr">
         <is>
           <t>심연(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="B135" s="14" t="n">
+      <c r="B135" s="25" t="n">
         <v>50011</v>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C135" s="4" t="inlineStr">
         <is>
           <t>여우 가죽</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E135" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F135" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G135" t="n">
+      <c r="F135" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G135" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="H135" s="4" t="inlineStr">
         <is>
           <t>야산(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="B136" s="14" t="n">
+      <c r="B136" s="25" t="n">
         <v>50012</v>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C136" s="4" t="inlineStr">
         <is>
           <t>멧돼지 엄니</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D136" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E136" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F136" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G136" t="n">
+      <c r="F136" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G136" s="25" t="n">
         <v>75</v>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="H136" s="4" t="inlineStr">
         <is>
           <t>야산(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="B137" s="14" t="n">
+      <c r="B137" s="25" t="n">
         <v>50013</v>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C137" s="4" t="inlineStr">
         <is>
           <t>사슴뿔</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D137" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E137" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F137" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G137" t="n">
+      <c r="F137" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G137" s="25" t="n">
         <v>180</v>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="H137" s="4" t="inlineStr">
         <is>
           <t>야산(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="B138" s="14" t="n">
+      <c r="B138" s="25" t="n">
         <v>50014</v>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C138" s="4" t="inlineStr">
         <is>
           <t>산군의 발톱</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D138" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E138" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F138" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G138" t="n">
+      <c r="F138" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G138" s="25" t="n">
         <v>450</v>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="H138" s="4" t="inlineStr">
         <is>
           <t>야산(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="B139" s="14" t="n">
+      <c r="B139" s="25" t="n">
         <v>50015</v>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C139" s="4" t="inlineStr">
         <is>
           <t>백호의 털</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E139" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F139" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G139" t="n">
+      <c r="F139" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G139" s="25" t="n">
         <v>1200</v>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="H139" s="4" t="inlineStr">
         <is>
           <t>야산(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="B140" s="14" t="n">
+      <c r="B140" s="25" t="n">
         <v>50016</v>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
         <is>
           <t>산신의 인장</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D140" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E140" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F140" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G140" t="n">
+      <c r="F140" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G140" s="25" t="n">
         <v>3000</v>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="H140" s="4" t="inlineStr">
         <is>
           <t>야산(Lv2)</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="B141" s="14" t="n">
+      <c r="B141" s="25" t="n">
         <v>50021</v>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C141" s="4" t="inlineStr">
         <is>
           <t>표범 가죽</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D141" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E141" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F141" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G141" t="n">
+      <c r="F141" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G141" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H141" s="4" t="inlineStr">
         <is>
           <t>깊은 숲(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="B142" s="14" t="n">
+      <c r="B142" s="25" t="n">
         <v>50022</v>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C142" s="4" t="inlineStr">
         <is>
           <t>큰뿔 사슴뿔</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D142" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E142" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F142" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G142" t="n">
+      <c r="F142" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G142" s="25" t="n">
         <v>225</v>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H142" s="4" t="inlineStr">
         <is>
           <t>깊은 숲(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="B143" s="14" t="n">
+      <c r="B143" s="25" t="n">
         <v>50023</v>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C143" s="4" t="inlineStr">
         <is>
           <t>곰의 이빨</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D143" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E143" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F143" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G143" t="n">
+      <c r="F143" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G143" s="25" t="n">
         <v>540</v>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="H143" s="4" t="inlineStr">
         <is>
           <t>깊은 숲(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="B144" s="14" t="n">
+      <c r="B144" s="25" t="n">
         <v>50024</v>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="C144" s="4" t="inlineStr">
         <is>
           <t>숲괴수의 발톱</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D144" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E144" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F144" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G144" t="n">
+      <c r="F144" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G144" s="25" t="n">
         <v>1350</v>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="H144" s="4" t="inlineStr">
         <is>
           <t>깊은 숲(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="B145" s="14" t="n">
+      <c r="B145" s="25" t="n">
         <v>50025</v>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C145" s="4" t="inlineStr">
         <is>
           <t>고대 짐승의 뼈</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D145" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="E145" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F145" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G145" t="n">
+      <c r="F145" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G145" s="25" t="n">
         <v>3600</v>
       </c>
-      <c r="H145" t="inlineStr">
+      <c r="H145" s="4" t="inlineStr">
         <is>
           <t>깊은 숲(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="B146" s="14" t="n">
+      <c r="B146" s="25" t="n">
         <v>50026</v>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C146" s="4" t="inlineStr">
         <is>
           <t>숲 지배자의 눈</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D146" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E146" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F146" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G146" t="n">
+      <c r="F146" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G146" s="25" t="n">
         <v>9000</v>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="H146" s="4" t="inlineStr">
         <is>
           <t>깊은 숲(Lv3)</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="B147" s="14" t="n">
+      <c r="B147" s="25" t="n">
         <v>50031</v>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="C147" s="4" t="inlineStr">
         <is>
           <t>설표 가죽</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D147" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E147" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F147" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G147" t="n">
+      <c r="F147" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G147" s="25" t="n">
         <v>270</v>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H147" s="4" t="inlineStr">
         <is>
           <t>설산(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="B148" s="14" t="n">
+      <c r="B148" s="25" t="n">
         <v>50032</v>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C148" s="4" t="inlineStr">
         <is>
           <t>얼음늑대 송곳니</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D148" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E148" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F148" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G148" t="n">
+      <c r="F148" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G148" s="25" t="n">
         <v>675</v>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="H148" s="4" t="inlineStr">
         <is>
           <t>설산(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="B149" s="14" t="n">
+      <c r="B149" s="25" t="n">
         <v>50033</v>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C149" s="4" t="inlineStr">
         <is>
           <t>서리곰 모피</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D149" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E149" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F149" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G149" t="n">
+      <c r="F149" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G149" s="25" t="n">
         <v>1620</v>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="H149" s="4" t="inlineStr">
         <is>
           <t>설산(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="B150" s="14" t="n">
+      <c r="B150" s="25" t="n">
         <v>50034</v>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C150" s="4" t="inlineStr">
         <is>
           <t>빙룡의 비늘</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D150" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E150" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F150" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G150" t="n">
+      <c r="F150" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G150" s="25" t="n">
         <v>4050</v>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="H150" s="4" t="inlineStr">
         <is>
           <t>설산(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="B151" s="14" t="n">
+      <c r="B151" s="25" t="n">
         <v>50035</v>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C151" s="4" t="inlineStr">
         <is>
           <t>설산 주인의 뿔</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D151" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E151" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F151" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G151" t="n">
+      <c r="F151" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G151" s="25" t="n">
         <v>10800</v>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="H151" s="4" t="inlineStr">
         <is>
           <t>설산(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="B152" s="14" t="n">
+      <c r="B152" s="25" t="n">
         <v>50036</v>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>영구동토의 심장</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D152" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E152" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F152" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G152" t="n">
+      <c r="F152" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G152" s="25" t="n">
         <v>27000</v>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="H152" s="4" t="inlineStr">
         <is>
           <t>설산(Lv4)</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="B153" s="14" t="n">
+      <c r="B153" s="25" t="n">
         <v>50041</v>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C153" s="4" t="inlineStr">
         <is>
           <t>마수의 가죽</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D153" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E153" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F153" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G153" t="n">
+      <c r="F153" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G153" s="25" t="n">
         <v>810</v>
       </c>
-      <c r="H153" t="inlineStr">
+      <c r="H153" s="4" t="inlineStr">
         <is>
           <t>마수의 영역(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="B154" s="14" t="n">
+      <c r="B154" s="25" t="n">
         <v>50042</v>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C154" s="4" t="inlineStr">
         <is>
           <t>마물의 뿔</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D154" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E154" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F154" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G154" t="n">
+      <c r="F154" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G154" s="25" t="n">
         <v>2025</v>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="H154" s="4" t="inlineStr">
         <is>
           <t>마수의 영역(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="B155" s="14" t="n">
+      <c r="B155" s="25" t="n">
         <v>50043</v>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C155" s="4" t="inlineStr">
         <is>
           <t>흉수의 송곳니</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D155" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="E155" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F155" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G155" t="n">
+      <c r="F155" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G155" s="25" t="n">
         <v>4860</v>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="H155" s="4" t="inlineStr">
         <is>
           <t>마수의 영역(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="B156" s="14" t="n">
+      <c r="B156" s="25" t="n">
         <v>50044</v>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C156" s="4" t="inlineStr">
         <is>
           <t>마수왕의 갈기</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="D156" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E156" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F156" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G156" t="n">
+      <c r="F156" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G156" s="25" t="n">
         <v>12150</v>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="H156" s="4" t="inlineStr">
         <is>
           <t>마수의 영역(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="B157" s="14" t="n">
+      <c r="B157" s="25" t="n">
         <v>50045</v>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C157" s="4" t="inlineStr">
         <is>
           <t>심연수의 눈</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D157" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="E157" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F157" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G157" t="n">
+      <c r="F157" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G157" s="25" t="n">
         <v>32400</v>
       </c>
-      <c r="H157" t="inlineStr">
+      <c r="H157" s="4" t="inlineStr">
         <is>
           <t>마수의 영역(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="B158" s="14" t="n">
+      <c r="B158" s="25" t="n">
         <v>50046</v>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C158" s="4" t="inlineStr">
         <is>
           <t>마신의 파편</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D158" s="4" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="E158" s="4" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F158" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G158" t="n">
+      <c r="F158" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G158" s="25" t="n">
         <v>81000</v>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="H158" s="4" t="inlineStr">
         <is>
           <t>마수의 영역(Lv5)</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="B159" s="14" t="n">
+      <c r="B159" s="25" t="n">
         <v>100001</v>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C159" s="4" t="inlineStr">
         <is>
           <t>유리 구슬</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D159" s="4" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E159" s="4" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F159" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G159" t="n">
+      <c r="F159" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G159" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="H159" s="4" t="inlineStr">
         <is>
           <t>가챠 전용(테스트)</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="B160" s="14" t="n">
+      <c r="B160" s="25" t="n">
         <v>100002</v>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C160" s="4" t="inlineStr">
         <is>
           <t>호박 구슬</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D160" s="4" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E160" s="4" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F160" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G160" t="n">
+      <c r="F160" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G160" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="H160" s="4" t="inlineStr">
         <is>
           <t>가챠 전용(테스트)</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="B161" s="14" t="n">
+      <c r="B161" s="25" t="n">
         <v>100003</v>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C161" s="4" t="inlineStr">
         <is>
           <t>진주 구슬</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D161" s="4" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E161" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F161" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G161" t="n">
+      <c r="F161" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G161" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="H161" s="4" t="inlineStr">
         <is>
           <t>가챠 전용(테스트)</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="B162" s="14" t="n">
+      <c r="B162" s="25" t="n">
         <v>100004</v>
       </c>
-      <c r="C162" t="inlineStr">
+      <c r="C162" s="4" t="inlineStr">
         <is>
           <t>오팔 구슬</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D162" s="4" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="E162" s="4" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F162" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G162" t="n">
+      <c r="F162" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G162" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="H162" s="4" t="inlineStr">
         <is>
           <t>가챠 전용(테스트)</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="B163" s="14" t="n">
+      <c r="B163" s="25" t="n">
         <v>100005</v>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C163" s="4" t="inlineStr">
         <is>
           <t>용안 구슬</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D163" s="4" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E163" s="4" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F163" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G163" t="n">
+      <c r="F163" s="25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G163" s="25" t="n">
         <v>400</v>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="H163" s="4" t="inlineStr">
         <is>
           <t>가챠 전용(테스트)</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="B164" s="16" t="n">
+      <c r="B164" s="26" t="n">
         <v>100006</v>
       </c>
-      <c r="C164" s="17" t="inlineStr">
+      <c r="C164" s="27" t="inlineStr">
         <is>
           <t>창세의 구슬</t>
         </is>
       </c>
-      <c r="D164" s="17" t="inlineStr">
+      <c r="D164" s="27" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="E164" s="17" t="inlineStr">
+      <c r="E164" s="27" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="F164" s="17" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G164" s="17" t="n">
+      <c r="F164" s="26" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G164" s="26" t="n">
         <v>1000</v>
       </c>
-      <c r="H164" s="17" t="inlineStr">
+      <c r="H164" s="27" t="inlineStr">
         <is>
           <t>가챠 전용(테스트)</t>
         </is>
@@ -5618,5 +5691,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -6148,12 +6148,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="7"/>
@@ -6853,6 +6853,181 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="19" t="n">
+        <v>100013</v>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>인챈트 원석</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>인챈트 부여 50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="19" t="n">
+        <v>100014</v>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>정제된 인챈트 원석</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>인챈트 부여 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="19" t="n">
+        <v>100015</v>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>인챈트 큐브</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>등급 판정 + 줄 재롤</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="19" t="n">
+        <v>100016</v>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>인챈트 확장석</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>3줄 확장 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="19" t="n">
+        <v>100017</v>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>정제된 인챈트 확장석</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>3줄 확장 확정</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -595,7 +595,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -6138,28 +6138,28 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="7"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="53" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6856,11 +6856,11 @@
     <row r="22">
       <c r="A22" s="11" t="n"/>
       <c r="B22" s="19" t="n">
-        <v>100013</v>
+        <v>100015</v>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>인챈트 원석</t>
+          <t>인챈트 큐브</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -6870,32 +6870,32 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F22" s="19" t="n">
         <v>9999</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H22" s="19" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
-          <t>인챈트 부여 50%</t>
+          <t>장비 능력치 칸 1개 다시 뽑기 — 등급 상승 기본 확률</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
       <c r="B23" s="19" t="n">
-        <v>100014</v>
+        <v>100018</v>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>정제된 인챈트 원석</t>
+          <t>상급 인챈트 큐브</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -6905,132 +6905,27 @@
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F23" s="19" t="n">
         <v>9999</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H23" s="19" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>인챈트 부여 확정</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="19" t="n">
-        <v>100015</v>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>인챈트 큐브</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G24" s="19" t="n">
-        <v>500</v>
-      </c>
-      <c r="H24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
-        <is>
-          <t>등급 판정 + 줄 재롤</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="19" t="n">
-        <v>100016</v>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>인챈트 확장석</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G25" s="19" t="n">
-        <v>300</v>
-      </c>
-      <c r="H25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>3줄 확장 30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="19" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>정제된 인챈트 확장석</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="n">
-        <v>9999</v>
-      </c>
-      <c r="G26" s="19" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H26" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="20" t="inlineStr">
-        <is>
-          <t>3줄 확장 확정</t>
+          <t>장비 능력치 칸 1개 다시 뽑기 — 등급 상승 확률 ×1.25</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -6148,7 +6148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6646,11 +6646,11 @@
     <row r="16">
       <c r="A16" s="11" t="n"/>
       <c r="B16" s="19" t="n">
-        <v>100007</v>
+        <v>100010</v>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>나무 상자</t>
+          <t>낡은 보물 지도</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -6664,28 +6664,28 @@
         </is>
       </c>
       <c r="F16" s="19" t="n">
-        <v>99</v>
+        <v>9999</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
-          <t>상자 — 여는 풀 6 · 채취 판정 공통 보상</t>
+          <t>나무 상자 전용 (임시 이름 · 용도 미정)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
       <c r="B17" s="19" t="n">
-        <v>100008</v>
+        <v>100011</v>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>은 상자</t>
+          <t>은빛 나침반</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -6699,28 +6699,28 @@
         </is>
       </c>
       <c r="F17" s="19" t="n">
-        <v>99</v>
+        <v>9999</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
-          <t>상자 — 여는 풀 7 · 채취 판정 공통 보상</t>
+          <t>은 상자 전용 (임시 이름 · 용도 미정)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n"/>
       <c r="B18" s="19" t="n">
-        <v>100009</v>
+        <v>100012</v>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>황금 상자</t>
+          <t>황금 열쇠</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -6734,28 +6734,28 @@
         </is>
       </c>
       <c r="F18" s="19" t="n">
-        <v>99</v>
+        <v>9999</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
-          <t>상자 — 여는 풀 8 · 채취 판정 공통 보상</t>
+          <t>황금 상자 전용 (임시 이름 · 용도 미정)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
       <c r="B19" s="19" t="n">
-        <v>100010</v>
+        <v>100015</v>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>낡은 보물 지도</t>
+          <t>인챈트 큐브</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -6765,32 +6765,32 @@
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F19" s="19" t="n">
         <v>9999</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H19" s="19" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
-          <t>나무 상자 전용 (임시 이름 · 용도 미정)</t>
+          <t>장비 능력치 칸 1개 다시 뽑기 — 등급 상승 기본 확률</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
       <c r="B20" s="19" t="n">
-        <v>100011</v>
+        <v>100018</v>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>은빛 나침반</t>
+          <t>상급 인챈트 큐브</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F20" s="19" t="n">
         <v>9999</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="H20" s="19" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
-          <t>은 상자 전용 (임시 이름 · 용도 미정)</t>
+          <t>장비 능력치 칸 1개 다시 뽑기 — 등급 상승 확률 ×1.25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
       <c r="B21" s="19" t="n">
-        <v>100012</v>
+        <v>100019</v>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>황금 열쇠</t>
+          <t>나무 상자 Lv1</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -6835,32 +6835,32 @@
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="F21" s="19" t="n">
-        <v>9999</v>
+        <v>99</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>500</v>
+        <v>54</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
-          <t>황금 상자 전용 (임시 이름 · 용도 미정)</t>
+          <t>상자 — 산업 Lv1 드롭 · 기대 가치 판정 ×10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
       <c r="B22" s="19" t="n">
-        <v>100015</v>
+        <v>100020</v>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>인챈트 큐브</t>
+          <t>은 상자 Lv1</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -6870,32 +6870,32 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F22" s="19" t="n">
-        <v>9999</v>
+        <v>99</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>500</v>
+        <v>163</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
-          <t>장비 능력치 칸 1개 다시 뽑기 — 등급 상승 기본 확률</t>
+          <t>상자 — 산업 Lv1 드롭 · 기대 가치 판정 ×30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
       <c r="B23" s="19" t="n">
-        <v>100018</v>
+        <v>100021</v>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>상급 인챈트 큐브</t>
+          <t>황금 상자 Lv1</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -6905,21 +6905,441 @@
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F23" s="19" t="n">
-        <v>9999</v>
+        <v>99</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>1000</v>
+        <v>542</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>장비 능력치 칸 1개 다시 뽑기 — 등급 상승 확률 ×1.25</t>
+          <t>상자 — 산업 Lv1 드롭 · 기대 가치 판정 ×100</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="19" t="n">
+        <v>100022</v>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv2</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>163</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>상자 — 산업 Lv2 드롭 · 기대 가치 판정 ×10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="19" t="n">
+        <v>100023</v>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>은 상자 Lv2</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>488</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>상자 — 산업 Lv2 드롭 · 기대 가치 판정 ×30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="19" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv2</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>1625</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>상자 — 산업 Lv2 드롭 · 기대 가치 판정 ×100</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="19" t="n">
+        <v>100025</v>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv3</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>488</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>상자 — 산업 Lv3 드롭 · 기대 가치 판정 ×10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="19" t="n">
+        <v>100026</v>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>은 상자 Lv3</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>1463</v>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>상자 — 산업 Lv3 드롭 · 기대 가치 판정 ×30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="19" t="n">
+        <v>100027</v>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv3</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>4876</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>상자 — 산업 Lv3 드롭 · 기대 가치 판정 ×100</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="19" t="n">
+        <v>100028</v>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv4</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>1463</v>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>상자 — 산업 Lv4 드롭 · 기대 가치 판정 ×10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="19" t="n">
+        <v>100029</v>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>은 상자 Lv4</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>4389</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>상자 — 산업 Lv4 드롭 · 기대 가치 판정 ×30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="19" t="n">
+        <v>100030</v>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv4</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>14629</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
+        <is>
+          <t>상자 — 산업 Lv4 드롭 · 기대 가치 판정 ×100</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="19" t="n">
+        <v>100031</v>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv5</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>4389</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>상자 — 산업 Lv5 드롭 · 기대 가치 판정 ×10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="19" t="n">
+        <v>100032</v>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>은 상자 Lv5</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>13166</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
+        <is>
+          <t>상자 — 산업 Lv5 드롭 · 기대 가치 판정 ×30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="19" t="n">
+        <v>100033</v>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv5</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>43886</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="I35" s="20" t="inlineStr">
+        <is>
+          <t>상자 — 산업 Lv5 드롭 · 기대 가치 판정 ×100</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="F21" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G21" s="19" t="n">
         <v>54</v>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="F22" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G22" s="19" t="n">
         <v>163</v>
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="F23" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G23" s="19" t="n">
         <v>542</v>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="F24" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G24" s="19" t="n">
         <v>163</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="F25" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G25" s="19" t="n">
         <v>488</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="F26" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G26" s="19" t="n">
         <v>1625</v>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="F27" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G27" s="19" t="n">
         <v>488</v>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="F28" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G28" s="19" t="n">
         <v>1463</v>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="F29" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G29" s="19" t="n">
         <v>4876</v>
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="F30" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G30" s="19" t="n">
         <v>1463</v>
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="F31" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G31" s="19" t="n">
         <v>4389</v>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="F32" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G32" s="19" t="n">
         <v>14629</v>
@@ -7259,7 +7259,7 @@
         </is>
       </c>
       <c r="F33" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G33" s="19" t="n">
         <v>4389</v>
@@ -7294,7 +7294,7 @@
         </is>
       </c>
       <c r="F34" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G34" s="19" t="n">
         <v>13166</v>
@@ -7329,7 +7329,7 @@
         </is>
       </c>
       <c r="F35" s="19" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G35" s="19" t="n">
         <v>43886</v>

--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -6159,7 +6159,7 @@
     <col width="11" customWidth="1" min="6" max="7"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="53" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
-          <t>장비 능력치 칸 1개 다시 뽑기 — 등급 상승 기본 확률</t>
+          <t>장비 능력치 칸 전부 다시 뽑기 · 확률로 인챈트 등급 한 단계 상승</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
-          <t>장비 능력치 칸 1개 다시 뽑기 — 등급 상승 확률 ×1.25</t>
+          <t>장비 능력치 칸 전부 다시 뽑기 · 인챈트 큐브보다 등급 상승 확률이 높다</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="F21" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="19" t="n">
         <v>54</v>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="F22" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G22" s="19" t="n">
         <v>163</v>
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="F23" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G23" s="19" t="n">
         <v>542</v>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="F24" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G24" s="19" t="n">
         <v>163</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="F25" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G25" s="19" t="n">
         <v>488</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="F26" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G26" s="19" t="n">
         <v>1625</v>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="F27" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G27" s="19" t="n">
         <v>488</v>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="F28" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G28" s="19" t="n">
         <v>1463</v>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="F29" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G29" s="19" t="n">
         <v>4876</v>
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="F30" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G30" s="19" t="n">
         <v>1463</v>
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="F31" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G31" s="19" t="n">
         <v>4389</v>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="F32" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G32" s="19" t="n">
         <v>14629</v>
@@ -7259,7 +7259,7 @@
         </is>
       </c>
       <c r="F33" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G33" s="19" t="n">
         <v>4389</v>
@@ -7294,7 +7294,7 @@
         </is>
       </c>
       <c r="F34" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G34" s="19" t="n">
         <v>13166</v>
@@ -7329,7 +7329,7 @@
         </is>
       </c>
       <c r="F35" s="19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G35" s="19" t="n">
         <v>43886</v>

--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I159"/>
+  <dimension ref="A1:J159"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -612,6 +612,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -624,6 +625,7 @@
       <c r="G1" s="11" t="n"/>
       <c r="H1" s="11" t="n"/>
       <c r="I1" s="11" t="n"/>
+      <c r="J1" s="11" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
@@ -671,6 +673,11 @@
           <t>메모</t>
         </is>
       </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>툴팁</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -718,6 +725,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -761,6 +773,11 @@
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -784,6 +801,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -799,6 +817,7 @@
       <c r="G6" s="15" t="n"/>
       <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -822,6 +841,11 @@
           <t>""</t>
         </is>
       </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -841,6 +865,7 @@
         </is>
       </c>
       <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="n"/>
@@ -882,6 +907,11 @@
       <c r="I9" s="17" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>Tooltip</t>
         </is>
       </c>
     </row>
@@ -919,6 +949,7 @@
           <t>개울(Lv1)</t>
         </is>
       </c>
+      <c r="J10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n"/>
@@ -954,6 +985,7 @@
           <t>개울(Lv1)</t>
         </is>
       </c>
+      <c r="J11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n"/>
@@ -989,6 +1021,7 @@
           <t>개울(Lv1)</t>
         </is>
       </c>
+      <c r="J12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n"/>
@@ -1024,6 +1057,7 @@
           <t>개울(Lv1)</t>
         </is>
       </c>
+      <c r="J13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>
@@ -1059,6 +1093,7 @@
           <t>개울(Lv1)</t>
         </is>
       </c>
+      <c r="J14" s="11" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="11" t="n"/>
@@ -1094,6 +1129,7 @@
           <t>개울(Lv1)</t>
         </is>
       </c>
+      <c r="J15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n"/>
@@ -1129,6 +1165,7 @@
           <t>텃밭(Lv1)</t>
         </is>
       </c>
+      <c r="J16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -1164,6 +1201,7 @@
           <t>텃밭(Lv1)</t>
         </is>
       </c>
+      <c r="J17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n"/>
@@ -1199,6 +1237,7 @@
           <t>텃밭(Lv1)</t>
         </is>
       </c>
+      <c r="J18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -1234,6 +1273,7 @@
           <t>텃밭(Lv1)</t>
         </is>
       </c>
+      <c r="J19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
@@ -1269,6 +1309,7 @@
           <t>텃밭(Lv1)</t>
         </is>
       </c>
+      <c r="J20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
@@ -1304,6 +1345,7 @@
           <t>텃밭(Lv1)</t>
         </is>
       </c>
+      <c r="J21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
@@ -1339,6 +1381,7 @@
           <t>잡목림(Lv1)</t>
         </is>
       </c>
+      <c r="J22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
@@ -1374,6 +1417,7 @@
           <t>잡목림(Lv1)</t>
         </is>
       </c>
+      <c r="J23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n"/>
@@ -1409,6 +1453,7 @@
           <t>잡목림(Lv1)</t>
         </is>
       </c>
+      <c r="J24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n"/>
@@ -1444,6 +1489,7 @@
           <t>잡목림(Lv1)</t>
         </is>
       </c>
+      <c r="J25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -1479,6 +1525,7 @@
           <t>잡목림(Lv1)</t>
         </is>
       </c>
+      <c r="J26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -1514,6 +1561,7 @@
           <t>잡목림(Lv1)</t>
         </is>
       </c>
+      <c r="J27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n"/>
@@ -1549,6 +1597,7 @@
           <t>노천 광산(Lv1)</t>
         </is>
       </c>
+      <c r="J28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n"/>
@@ -1584,6 +1633,7 @@
           <t>노천 광산(Lv1)</t>
         </is>
       </c>
+      <c r="J29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n"/>
@@ -1619,6 +1669,7 @@
           <t>노천 광산(Lv1)</t>
         </is>
       </c>
+      <c r="J30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n"/>
@@ -1654,6 +1705,7 @@
           <t>노천 광산(Lv1)</t>
         </is>
       </c>
+      <c r="J31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n"/>
@@ -1689,6 +1741,7 @@
           <t>노천 광산(Lv1)</t>
         </is>
       </c>
+      <c r="J32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n"/>
@@ -1724,6 +1777,7 @@
           <t>노천 광산(Lv1)</t>
         </is>
       </c>
+      <c r="J33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n"/>
@@ -1759,6 +1813,7 @@
           <t>들판(Lv1)</t>
         </is>
       </c>
+      <c r="J34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n"/>
@@ -1794,6 +1849,7 @@
           <t>들판(Lv1)</t>
         </is>
       </c>
+      <c r="J35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n"/>
@@ -1829,6 +1885,7 @@
           <t>들판(Lv1)</t>
         </is>
       </c>
+      <c r="J36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n"/>
@@ -1864,6 +1921,7 @@
           <t>들판(Lv1)</t>
         </is>
       </c>
+      <c r="J37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n"/>
@@ -1899,6 +1957,7 @@
           <t>들판(Lv1)</t>
         </is>
       </c>
+      <c r="J38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n"/>
@@ -1934,6 +1993,7 @@
           <t>들판(Lv1)</t>
         </is>
       </c>
+      <c r="J39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n"/>
@@ -1969,6 +2029,7 @@
           <t>저수지(Lv2)</t>
         </is>
       </c>
+      <c r="J40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="n"/>
@@ -2004,6 +2065,7 @@
           <t>저수지(Lv2)</t>
         </is>
       </c>
+      <c r="J41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="n"/>
@@ -2039,6 +2101,7 @@
           <t>저수지(Lv2)</t>
         </is>
       </c>
+      <c r="J42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="n"/>
@@ -2074,6 +2137,7 @@
           <t>저수지(Lv2)</t>
         </is>
       </c>
+      <c r="J43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="n"/>
@@ -2109,6 +2173,7 @@
           <t>저수지(Lv2)</t>
         </is>
       </c>
+      <c r="J44" s="11" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="n"/>
@@ -2144,6 +2209,7 @@
           <t>저수지(Lv2)</t>
         </is>
       </c>
+      <c r="J45" s="11" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="n"/>
@@ -2179,6 +2245,7 @@
           <t>강 하류(Lv3)</t>
         </is>
       </c>
+      <c r="J46" s="11" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="n"/>
@@ -2214,6 +2281,7 @@
           <t>강 하류(Lv3)</t>
         </is>
       </c>
+      <c r="J47" s="11" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="n"/>
@@ -2249,6 +2317,7 @@
           <t>강 하류(Lv3)</t>
         </is>
       </c>
+      <c r="J48" s="11" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="n"/>
@@ -2284,6 +2353,7 @@
           <t>강 하류(Lv3)</t>
         </is>
       </c>
+      <c r="J49" s="11" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="n"/>
@@ -2319,6 +2389,7 @@
           <t>강 하류(Lv3)</t>
         </is>
       </c>
+      <c r="J50" s="11" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="n"/>
@@ -2354,6 +2425,7 @@
           <t>강 하류(Lv3)</t>
         </is>
       </c>
+      <c r="J51" s="11" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n"/>
@@ -2389,6 +2461,7 @@
           <t>호수(Lv4)</t>
         </is>
       </c>
+      <c r="J52" s="11" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n"/>
@@ -2424,6 +2497,7 @@
           <t>호수(Lv4)</t>
         </is>
       </c>
+      <c r="J53" s="11" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n"/>
@@ -2459,6 +2533,7 @@
           <t>호수(Lv4)</t>
         </is>
       </c>
+      <c r="J54" s="11" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="n"/>
@@ -2494,6 +2569,7 @@
           <t>호수(Lv4)</t>
         </is>
       </c>
+      <c r="J55" s="11" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="n"/>
@@ -2529,6 +2605,7 @@
           <t>호수(Lv4)</t>
         </is>
       </c>
+      <c r="J56" s="11" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="n"/>
@@ -2564,6 +2641,7 @@
           <t>호수(Lv4)</t>
         </is>
       </c>
+      <c r="J57" s="11" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n"/>
@@ -2599,6 +2677,7 @@
           <t>심해(Lv5)</t>
         </is>
       </c>
+      <c r="J58" s="11" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n"/>
@@ -2634,6 +2713,7 @@
           <t>심해(Lv5)</t>
         </is>
       </c>
+      <c r="J59" s="11" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="n"/>
@@ -2669,6 +2749,7 @@
           <t>심해(Lv5)</t>
         </is>
       </c>
+      <c r="J60" s="11" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n"/>
@@ -2704,6 +2785,7 @@
           <t>심해(Lv5)</t>
         </is>
       </c>
+      <c r="J61" s="11" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n"/>
@@ -2739,6 +2821,7 @@
           <t>심해(Lv5)</t>
         </is>
       </c>
+      <c r="J62" s="11" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="n"/>
@@ -2774,6 +2857,7 @@
           <t>심해(Lv5)</t>
         </is>
       </c>
+      <c r="J63" s="11" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n"/>
@@ -2809,6 +2893,7 @@
           <t>밭(Lv2)</t>
         </is>
       </c>
+      <c r="J64" s="11" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n"/>
@@ -2844,6 +2929,7 @@
           <t>밭(Lv2)</t>
         </is>
       </c>
+      <c r="J65" s="11" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="n"/>
@@ -2879,6 +2965,7 @@
           <t>밭(Lv2)</t>
         </is>
       </c>
+      <c r="J66" s="11" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n"/>
@@ -2914,6 +3001,7 @@
           <t>밭(Lv2)</t>
         </is>
       </c>
+      <c r="J67" s="11" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n"/>
@@ -2949,6 +3037,7 @@
           <t>밭(Lv2)</t>
         </is>
       </c>
+      <c r="J68" s="11" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n"/>
@@ -2984,6 +3073,7 @@
           <t>밭(Lv2)</t>
         </is>
       </c>
+      <c r="J69" s="11" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="n"/>
@@ -3019,6 +3109,7 @@
           <t>농장(Lv3)</t>
         </is>
       </c>
+      <c r="J70" s="11" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="n"/>
@@ -3054,6 +3145,7 @@
           <t>농장(Lv3)</t>
         </is>
       </c>
+      <c r="J71" s="11" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="n"/>
@@ -3089,6 +3181,7 @@
           <t>농장(Lv3)</t>
         </is>
       </c>
+      <c r="J72" s="11" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n"/>
@@ -3124,6 +3217,7 @@
           <t>농장(Lv3)</t>
         </is>
       </c>
+      <c r="J73" s="11" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="n"/>
@@ -3159,6 +3253,7 @@
           <t>농장(Lv3)</t>
         </is>
       </c>
+      <c r="J74" s="11" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n"/>
@@ -3194,6 +3289,7 @@
           <t>농장(Lv3)</t>
         </is>
       </c>
+      <c r="J75" s="11" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n"/>
@@ -3229,6 +3325,7 @@
           <t>대농장(Lv4)</t>
         </is>
       </c>
+      <c r="J76" s="11" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n"/>
@@ -3264,6 +3361,7 @@
           <t>대농장(Lv4)</t>
         </is>
       </c>
+      <c r="J77" s="11" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n"/>
@@ -3299,6 +3397,7 @@
           <t>대농장(Lv4)</t>
         </is>
       </c>
+      <c r="J78" s="11" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="n"/>
@@ -3334,6 +3433,7 @@
           <t>대농장(Lv4)</t>
         </is>
       </c>
+      <c r="J79" s="11" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n"/>
@@ -3369,6 +3469,7 @@
           <t>대농장(Lv4)</t>
         </is>
       </c>
+      <c r="J80" s="11" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="n"/>
@@ -3404,6 +3505,7 @@
           <t>대농장(Lv4)</t>
         </is>
       </c>
+      <c r="J81" s="11" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="n"/>
@@ -3439,6 +3541,7 @@
           <t>신성한 대지(Lv5)</t>
         </is>
       </c>
+      <c r="J82" s="11" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="n"/>
@@ -3474,6 +3577,7 @@
           <t>신성한 대지(Lv5)</t>
         </is>
       </c>
+      <c r="J83" s="11" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="n"/>
@@ -3509,6 +3613,7 @@
           <t>신성한 대지(Lv5)</t>
         </is>
       </c>
+      <c r="J84" s="11" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="n"/>
@@ -3544,6 +3649,7 @@
           <t>신성한 대지(Lv5)</t>
         </is>
       </c>
+      <c r="J85" s="11" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="n"/>
@@ -3579,6 +3685,7 @@
           <t>신성한 대지(Lv5)</t>
         </is>
       </c>
+      <c r="J86" s="11" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="n"/>
@@ -3614,6 +3721,7 @@
           <t>신성한 대지(Lv5)</t>
         </is>
       </c>
+      <c r="J87" s="11" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="n"/>
@@ -3649,6 +3757,7 @@
           <t>소나무 숲(Lv2)</t>
         </is>
       </c>
+      <c r="J88" s="11" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n"/>
@@ -3684,6 +3793,7 @@
           <t>소나무 숲(Lv2)</t>
         </is>
       </c>
+      <c r="J89" s="11" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n"/>
@@ -3719,6 +3829,7 @@
           <t>소나무 숲(Lv2)</t>
         </is>
       </c>
+      <c r="J90" s="11" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="n"/>
@@ -3754,6 +3865,7 @@
           <t>소나무 숲(Lv2)</t>
         </is>
       </c>
+      <c r="J91" s="11" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="11" t="n"/>
@@ -3789,6 +3901,7 @@
           <t>소나무 숲(Lv2)</t>
         </is>
       </c>
+      <c r="J92" s="11" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="n"/>
@@ -3824,6 +3937,7 @@
           <t>소나무 숲(Lv2)</t>
         </is>
       </c>
+      <c r="J93" s="11" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="n"/>
@@ -3859,6 +3973,7 @@
           <t>참나무 숲(Lv3)</t>
         </is>
       </c>
+      <c r="J94" s="11" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="n"/>
@@ -3894,6 +4009,7 @@
           <t>참나무 숲(Lv3)</t>
         </is>
       </c>
+      <c r="J95" s="11" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="11" t="n"/>
@@ -3929,6 +4045,7 @@
           <t>참나무 숲(Lv3)</t>
         </is>
       </c>
+      <c r="J96" s="11" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="n"/>
@@ -3964,6 +4081,7 @@
           <t>참나무 숲(Lv3)</t>
         </is>
       </c>
+      <c r="J97" s="11" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="n"/>
@@ -3999,6 +4117,7 @@
           <t>참나무 숲(Lv3)</t>
         </is>
       </c>
+      <c r="J98" s="11" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="11" t="n"/>
@@ -4034,6 +4153,7 @@
           <t>참나무 숲(Lv3)</t>
         </is>
       </c>
+      <c r="J99" s="11" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="11" t="n"/>
@@ -4069,6 +4189,7 @@
           <t>흑림(Lv4)</t>
         </is>
       </c>
+      <c r="J100" s="11" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="n"/>
@@ -4104,6 +4225,7 @@
           <t>흑림(Lv4)</t>
         </is>
       </c>
+      <c r="J101" s="11" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="n"/>
@@ -4139,6 +4261,7 @@
           <t>흑림(Lv4)</t>
         </is>
       </c>
+      <c r="J102" s="11" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="11" t="n"/>
@@ -4174,6 +4297,7 @@
           <t>흑림(Lv4)</t>
         </is>
       </c>
+      <c r="J103" s="11" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="11" t="n"/>
@@ -4209,6 +4333,7 @@
           <t>흑림(Lv4)</t>
         </is>
       </c>
+      <c r="J104" s="11" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="11" t="n"/>
@@ -4244,6 +4369,7 @@
           <t>흑림(Lv4)</t>
         </is>
       </c>
+      <c r="J105" s="11" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="n"/>
@@ -4279,6 +4405,7 @@
           <t>세계수 뿌리(Lv5)</t>
         </is>
       </c>
+      <c r="J106" s="11" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="11" t="n"/>
@@ -4314,6 +4441,7 @@
           <t>세계수 뿌리(Lv5)</t>
         </is>
       </c>
+      <c r="J107" s="11" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="n"/>
@@ -4349,6 +4477,7 @@
           <t>세계수 뿌리(Lv5)</t>
         </is>
       </c>
+      <c r="J108" s="11" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="11" t="n"/>
@@ -4384,6 +4513,7 @@
           <t>세계수 뿌리(Lv5)</t>
         </is>
       </c>
+      <c r="J109" s="11" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="n"/>
@@ -4419,6 +4549,7 @@
           <t>세계수 뿌리(Lv5)</t>
         </is>
       </c>
+      <c r="J110" s="11" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="11" t="n"/>
@@ -4454,6 +4585,7 @@
           <t>세계수 뿌리(Lv5)</t>
         </is>
       </c>
+      <c r="J111" s="11" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="11" t="n"/>
@@ -4489,6 +4621,7 @@
           <t>갱도(Lv2)</t>
         </is>
       </c>
+      <c r="J112" s="11" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="11" t="n"/>
@@ -4524,6 +4657,7 @@
           <t>갱도(Lv2)</t>
         </is>
       </c>
+      <c r="J113" s="11" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="11" t="n"/>
@@ -4559,6 +4693,7 @@
           <t>갱도(Lv2)</t>
         </is>
       </c>
+      <c r="J114" s="11" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="11" t="n"/>
@@ -4594,6 +4729,7 @@
           <t>갱도(Lv2)</t>
         </is>
       </c>
+      <c r="J115" s="11" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="11" t="n"/>
@@ -4629,6 +4765,7 @@
           <t>갱도(Lv2)</t>
         </is>
       </c>
+      <c r="J116" s="11" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="n"/>
@@ -4664,6 +4801,7 @@
           <t>갱도(Lv2)</t>
         </is>
       </c>
+      <c r="J117" s="11" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="11" t="n"/>
@@ -4699,6 +4837,7 @@
           <t>심층 갱도(Lv3)</t>
         </is>
       </c>
+      <c r="J118" s="11" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="11" t="n"/>
@@ -4734,6 +4873,7 @@
           <t>심층 갱도(Lv3)</t>
         </is>
       </c>
+      <c r="J119" s="11" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="n"/>
@@ -4769,6 +4909,7 @@
           <t>심층 갱도(Lv3)</t>
         </is>
       </c>
+      <c r="J120" s="11" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="11" t="n"/>
@@ -4804,6 +4945,7 @@
           <t>심층 갱도(Lv3)</t>
         </is>
       </c>
+      <c r="J121" s="11" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="n"/>
@@ -4839,6 +4981,7 @@
           <t>심층 갱도(Lv3)</t>
         </is>
       </c>
+      <c r="J122" s="11" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="11" t="n"/>
@@ -4874,6 +5017,7 @@
           <t>심층 갱도(Lv3)</t>
         </is>
       </c>
+      <c r="J123" s="11" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="n"/>
@@ -4909,6 +5053,7 @@
           <t>지하 대공동(Lv4)</t>
         </is>
       </c>
+      <c r="J124" s="11" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="11" t="n"/>
@@ -4944,6 +5089,7 @@
           <t>지하 대공동(Lv4)</t>
         </is>
       </c>
+      <c r="J125" s="11" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="n"/>
@@ -4979,6 +5125,7 @@
           <t>지하 대공동(Lv4)</t>
         </is>
       </c>
+      <c r="J126" s="11" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="n"/>
@@ -5014,6 +5161,7 @@
           <t>지하 대공동(Lv4)</t>
         </is>
       </c>
+      <c r="J127" s="11" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="11" t="n"/>
@@ -5049,6 +5197,7 @@
           <t>지하 대공동(Lv4)</t>
         </is>
       </c>
+      <c r="J128" s="11" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="11" t="n"/>
@@ -5084,6 +5233,7 @@
           <t>지하 대공동(Lv4)</t>
         </is>
       </c>
+      <c r="J129" s="11" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="11" t="n"/>
@@ -5119,6 +5269,7 @@
           <t>심연(Lv5)</t>
         </is>
       </c>
+      <c r="J130" s="11" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="11" t="n"/>
@@ -5154,6 +5305,7 @@
           <t>심연(Lv5)</t>
         </is>
       </c>
+      <c r="J131" s="11" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="11" t="n"/>
@@ -5189,6 +5341,7 @@
           <t>심연(Lv5)</t>
         </is>
       </c>
+      <c r="J132" s="11" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="11" t="n"/>
@@ -5224,6 +5377,7 @@
           <t>심연(Lv5)</t>
         </is>
       </c>
+      <c r="J133" s="11" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="11" t="n"/>
@@ -5259,6 +5413,7 @@
           <t>심연(Lv5)</t>
         </is>
       </c>
+      <c r="J134" s="11" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="n"/>
@@ -5294,6 +5449,7 @@
           <t>심연(Lv5)</t>
         </is>
       </c>
+      <c r="J135" s="11" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="11" t="n"/>
@@ -5329,6 +5485,7 @@
           <t>야산(Lv2)</t>
         </is>
       </c>
+      <c r="J136" s="11" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="11" t="n"/>
@@ -5364,6 +5521,7 @@
           <t>야산(Lv2)</t>
         </is>
       </c>
+      <c r="J137" s="11" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="11" t="n"/>
@@ -5399,6 +5557,7 @@
           <t>야산(Lv2)</t>
         </is>
       </c>
+      <c r="J138" s="11" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="n"/>
@@ -5434,6 +5593,7 @@
           <t>야산(Lv2)</t>
         </is>
       </c>
+      <c r="J139" s="11" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="11" t="n"/>
@@ -5469,6 +5629,7 @@
           <t>야산(Lv2)</t>
         </is>
       </c>
+      <c r="J140" s="11" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="11" t="n"/>
@@ -5504,6 +5665,7 @@
           <t>야산(Lv2)</t>
         </is>
       </c>
+      <c r="J141" s="11" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="11" t="n"/>
@@ -5539,6 +5701,7 @@
           <t>깊은 숲(Lv3)</t>
         </is>
       </c>
+      <c r="J142" s="11" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="n"/>
@@ -5574,6 +5737,7 @@
           <t>깊은 숲(Lv3)</t>
         </is>
       </c>
+      <c r="J143" s="11" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="11" t="n"/>
@@ -5609,6 +5773,7 @@
           <t>깊은 숲(Lv3)</t>
         </is>
       </c>
+      <c r="J144" s="11" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="11" t="n"/>
@@ -5644,6 +5809,7 @@
           <t>깊은 숲(Lv3)</t>
         </is>
       </c>
+      <c r="J145" s="11" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="11" t="n"/>
@@ -5679,6 +5845,7 @@
           <t>깊은 숲(Lv3)</t>
         </is>
       </c>
+      <c r="J146" s="11" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="11" t="n"/>
@@ -5714,6 +5881,7 @@
           <t>깊은 숲(Lv3)</t>
         </is>
       </c>
+      <c r="J147" s="11" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="11" t="n"/>
@@ -5749,6 +5917,7 @@
           <t>설산(Lv4)</t>
         </is>
       </c>
+      <c r="J148" s="11" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="11" t="n"/>
@@ -5784,6 +5953,7 @@
           <t>설산(Lv4)</t>
         </is>
       </c>
+      <c r="J149" s="11" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="11" t="n"/>
@@ -5819,6 +5989,7 @@
           <t>설산(Lv4)</t>
         </is>
       </c>
+      <c r="J150" s="11" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="n"/>
@@ -5854,6 +6025,7 @@
           <t>설산(Lv4)</t>
         </is>
       </c>
+      <c r="J151" s="11" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="n"/>
@@ -5889,6 +6061,7 @@
           <t>설산(Lv4)</t>
         </is>
       </c>
+      <c r="J152" s="11" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="11" t="n"/>
@@ -5924,6 +6097,7 @@
           <t>설산(Lv4)</t>
         </is>
       </c>
+      <c r="J153" s="11" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="11" t="n"/>
@@ -5959,6 +6133,7 @@
           <t>마수의 영역(Lv5)</t>
         </is>
       </c>
+      <c r="J154" s="11" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="11" t="n"/>
@@ -5994,6 +6169,7 @@
           <t>마수의 영역(Lv5)</t>
         </is>
       </c>
+      <c r="J155" s="11" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="11" t="n"/>
@@ -6029,6 +6205,7 @@
           <t>마수의 영역(Lv5)</t>
         </is>
       </c>
+      <c r="J156" s="11" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="11" t="n"/>
@@ -6064,6 +6241,7 @@
           <t>마수의 영역(Lv5)</t>
         </is>
       </c>
+      <c r="J157" s="11" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="11" t="n"/>
@@ -6099,6 +6277,7 @@
           <t>마수의 영역(Lv5)</t>
         </is>
       </c>
+      <c r="J158" s="11" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="11" t="n"/>
@@ -6134,6 +6313,7 @@
           <t>마수의 영역(Lv5)</t>
         </is>
       </c>
+      <c r="J159" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6148,7 +6328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6160,6 +6340,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6172,6 +6353,7 @@
       <c r="G1" s="11" t="n"/>
       <c r="H1" s="11" t="n"/>
       <c r="I1" s="11" t="n"/>
+      <c r="J1" s="11" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
@@ -6219,6 +6401,11 @@
           <t>메모</t>
         </is>
       </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>툴팁</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -6266,6 +6453,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -6309,6 +6501,11 @@
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -6332,6 +6529,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -6347,6 +6545,7 @@
       <c r="G6" s="15" t="n"/>
       <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -6370,6 +6569,11 @@
           <t>""</t>
         </is>
       </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -6389,6 +6593,7 @@
         </is>
       </c>
       <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="n"/>
@@ -6430,6 +6635,11 @@
       <c r="I9" s="17" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>Tooltip</t>
         </is>
       </c>
     </row>
@@ -6467,6 +6677,7 @@
           <t>가챠 전용(테스트)</t>
         </is>
       </c>
+      <c r="J10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n"/>
@@ -6502,6 +6713,7 @@
           <t>가챠 전용(테스트)</t>
         </is>
       </c>
+      <c r="J11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n"/>
@@ -6537,6 +6749,7 @@
           <t>가챠 전용(테스트)</t>
         </is>
       </c>
+      <c r="J12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n"/>
@@ -6572,6 +6785,7 @@
           <t>가챠 전용(테스트)</t>
         </is>
       </c>
+      <c r="J13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>
@@ -6607,6 +6821,7 @@
           <t>가챠 전용(테스트)</t>
         </is>
       </c>
+      <c r="J14" s="11" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="11" t="n"/>
@@ -6642,6 +6857,7 @@
           <t>가챠 전용(테스트)</t>
         </is>
       </c>
+      <c r="J15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n"/>
@@ -6677,6 +6893,7 @@
           <t>나무 상자 전용 (임시 이름 · 용도 미정)</t>
         </is>
       </c>
+      <c r="J16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -6712,6 +6929,7 @@
           <t>은 상자 전용 (임시 이름 · 용도 미정)</t>
         </is>
       </c>
+      <c r="J17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n"/>
@@ -6747,6 +6965,7 @@
           <t>황금 상자 전용 (임시 이름 · 용도 미정)</t>
         </is>
       </c>
+      <c r="J18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -6782,6 +7001,7 @@
           <t>장비 능력치 칸 전부 다시 뽑기 · 확률로 인챈트 등급 한 단계 상승</t>
         </is>
       </c>
+      <c r="J19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
@@ -6817,6 +7037,7 @@
           <t>장비 능력치 칸 전부 다시 뽑기 · 인챈트 큐브보다 등급 상승 확률이 높다</t>
         </is>
       </c>
+      <c r="J20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
@@ -6852,6 +7073,7 @@
           <t>상자 — 산업 Lv1 드롭 · 기대 가치 판정 ×10</t>
         </is>
       </c>
+      <c r="J21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
@@ -6887,6 +7109,7 @@
           <t>상자 — 산업 Lv1 드롭 · 기대 가치 판정 ×30</t>
         </is>
       </c>
+      <c r="J22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
@@ -6922,6 +7145,7 @@
           <t>상자 — 산업 Lv1 드롭 · 기대 가치 판정 ×100</t>
         </is>
       </c>
+      <c r="J23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n"/>
@@ -6957,6 +7181,7 @@
           <t>상자 — 산업 Lv2 드롭 · 기대 가치 판정 ×10</t>
         </is>
       </c>
+      <c r="J24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n"/>
@@ -6992,6 +7217,7 @@
           <t>상자 — 산업 Lv2 드롭 · 기대 가치 판정 ×30</t>
         </is>
       </c>
+      <c r="J25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -7027,6 +7253,7 @@
           <t>상자 — 산업 Lv2 드롭 · 기대 가치 판정 ×100</t>
         </is>
       </c>
+      <c r="J26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -7062,6 +7289,7 @@
           <t>상자 — 산업 Lv3 드롭 · 기대 가치 판정 ×10</t>
         </is>
       </c>
+      <c r="J27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n"/>
@@ -7097,6 +7325,7 @@
           <t>상자 — 산업 Lv3 드롭 · 기대 가치 판정 ×30</t>
         </is>
       </c>
+      <c r="J28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n"/>
@@ -7132,6 +7361,7 @@
           <t>상자 — 산업 Lv3 드롭 · 기대 가치 판정 ×100</t>
         </is>
       </c>
+      <c r="J29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n"/>
@@ -7167,6 +7397,7 @@
           <t>상자 — 산업 Lv4 드롭 · 기대 가치 판정 ×10</t>
         </is>
       </c>
+      <c r="J30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n"/>
@@ -7202,6 +7433,7 @@
           <t>상자 — 산업 Lv4 드롭 · 기대 가치 판정 ×30</t>
         </is>
       </c>
+      <c r="J31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n"/>
@@ -7237,6 +7469,7 @@
           <t>상자 — 산업 Lv4 드롭 · 기대 가치 판정 ×100</t>
         </is>
       </c>
+      <c r="J32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n"/>
@@ -7272,6 +7505,7 @@
           <t>상자 — 산업 Lv5 드롭 · 기대 가치 판정 ×10</t>
         </is>
       </c>
+      <c r="J33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n"/>
@@ -7307,6 +7541,7 @@
           <t>상자 — 산업 Lv5 드롭 · 기대 가치 판정 ×30</t>
         </is>
       </c>
+      <c r="J34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n"/>
@@ -7342,6 +7577,7 @@
           <t>상자 — 산업 Lv5 드롭 · 기대 가치 판정 ×100</t>
         </is>
       </c>
+      <c r="J35" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -6328,7 +6328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
-          <t>나무 상자 전용 (임시 이름 · 용도 미정)</t>
+          <t>지정 슬롯 다음 1회 판정 즉시 완료 (시간 스킵)</t>
         </is>
       </c>
       <c r="J16" s="11" t="n"/>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
-          <t>은 상자 전용 (임시 이름 · 용도 미정)</t>
+          <t>지정 슬롯 다음 20회 판정 동안 상자 드롭 확률 +100% (2배)</t>
         </is>
       </c>
       <c r="J17" s="11" t="n"/>
@@ -6958,11 +6958,11 @@
         <v>500</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
-          <t>황금 상자 전용 (임시 이름 · 용도 미정)</t>
+          <t>비밀 금고(GachaId 24) 1회 개봉 (고등급 장비·큐브 묶음 확정)</t>
         </is>
       </c>
       <c r="J18" s="11" t="n"/>
@@ -7578,6 +7578,258 @@
         </is>
       </c>
       <c r="J35" s="11" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="19" t="n">
+        <v>100041</v>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>성장의 비약 (소)</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="20" t="inlineStr">
+        <is>
+          <t>캐릭터 경험치 +100 Exp 즉시 획득</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="n"/>
+      <c r="B37" s="19" t="n">
+        <v>100042</v>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중)</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="20" t="inlineStr">
+        <is>
+          <t>캐릭터 경험치 +500 Exp 즉시 획득</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="n"/>
+      <c r="B38" s="19" t="n">
+        <v>100043</v>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>성장의 비약 (대)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G38" s="19" t="n">
+        <v>1250</v>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="20" t="inlineStr">
+        <is>
+          <t>캐릭터 경험치 +2,500 Exp 즉시 획득</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="n"/>
+      <c r="B39" s="19" t="n">
+        <v>100044</v>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>신속의 영약</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>지정 슬롯 다음 20회 판정 동안 작업속도 +30% (+300‰ 가산)</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="n"/>
+      <c r="B40" s="19" t="n">
+        <v>100045</v>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>풍요의 영약</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G40" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t>지정 슬롯 다음 20회 판정 동안 자원 산출량 +30% (+300‰ 가산)</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="n"/>
+      <c r="B41" s="19" t="n">
+        <v>100046</v>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>망각의 묘약</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
+        <is>
+          <t>투자된 계정 특성 포인트 전액 초기화</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="19" t="n">
+        <v>100050</v>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>마력의 파편</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="20" t="inlineStr">
+        <is>
+          <t>남는 장비를 분해하여 얻은 마력의 결정체. 큐브나 영약으로 교환할 수 있다</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -605,7 +605,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="7"/>
@@ -922,12 +922,12 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>붕어</t>
+          <t>깨진 토기 조각</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
-          <t>개울(Lv1)</t>
+          <t>옛 집터(Lv1)</t>
         </is>
       </c>
       <c r="J10" s="11" t="n"/>
@@ -958,12 +958,12 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>잉어</t>
+          <t>녹슨 동전</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>개울(Lv1)</t>
+          <t>옛 집터(Lv1)</t>
         </is>
       </c>
       <c r="J11" s="11" t="n"/>
@@ -994,12 +994,12 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>월척 붕어</t>
+          <t>흙 묻은 구슬</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>개울(Lv1)</t>
+          <t>옛 집터(Lv1)</t>
         </is>
       </c>
       <c r="J12" s="11" t="n"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>향어</t>
+          <t>청동 거울</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>개울(Lv1)</t>
+          <t>옛 집터(Lv1)</t>
         </is>
       </c>
       <c r="J13" s="11" t="n"/>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>대물 잉어</t>
+          <t>옛 장인의 도장</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>개울(Lv1)</t>
+          <t>옛 집터(Lv1)</t>
         </is>
       </c>
       <c r="J14" s="11" t="n"/>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>전설의 잉어</t>
+          <t>개척자의 일지</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
-          <t>개울(Lv1)</t>
+          <t>옛 집터(Lv1)</t>
         </is>
       </c>
       <c r="J15" s="11" t="n"/>
@@ -2002,12 +2002,12 @@
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>피라미</t>
+          <t>부러진 화살촉</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
-          <t>저수지(Lv2)</t>
+          <t>무너진 성벽(Lv2)</t>
         </is>
       </c>
       <c r="J40" s="11" t="n"/>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>메기</t>
+          <t>녹슨 투구</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="I41" s="20" t="inlineStr">
         <is>
-          <t>저수지(Lv2)</t>
+          <t>무너진 성벽(Lv2)</t>
         </is>
       </c>
       <c r="J41" s="11" t="n"/>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>가물치</t>
+          <t>성벽 문장석</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
-          <t>저수지(Lv2)</t>
+          <t>무너진 성벽(Lv2)</t>
         </is>
       </c>
       <c r="J42" s="11" t="n"/>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C43" s="20" t="inlineStr">
         <is>
-          <t>백년 메기</t>
+          <t>기사의 방패</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>저수지(Lv2)</t>
+          <t>무너진 성벽(Lv2)</t>
         </is>
       </c>
       <c r="J43" s="11" t="n"/>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>저수지의 주인</t>
+          <t>성주의 인장</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
-          <t>저수지(Lv2)</t>
+          <t>무너진 성벽(Lv2)</t>
         </is>
       </c>
       <c r="J44" s="11" t="n"/>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
-          <t>용왕의 사자</t>
+          <t>수호기사의 검</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E45" s="20" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
-          <t>저수지(Lv2)</t>
+          <t>무너진 성벽(Lv2)</t>
         </is>
       </c>
       <c r="J45" s="11" t="n"/>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="C46" s="20" t="inlineStr">
         <is>
-          <t>모래무지</t>
+          <t>깨진 석판</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
-          <t>강 하류(Lv3)</t>
+          <t>고대 신전(Lv3)</t>
         </is>
       </c>
       <c r="J46" s="11" t="n"/>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="C47" s="20" t="inlineStr">
         <is>
-          <t>쏘가리</t>
+          <t>향로 조각</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E47" s="20" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I47" s="20" t="inlineStr">
         <is>
-          <t>강 하류(Lv3)</t>
+          <t>고대 신전(Lv3)</t>
         </is>
       </c>
       <c r="J47" s="11" t="n"/>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>황금 잉어</t>
+          <t>신전 촛대</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="I48" s="20" t="inlineStr">
         <is>
-          <t>강 하류(Lv3)</t>
+          <t>고대 신전(Lv3)</t>
         </is>
       </c>
       <c r="J48" s="11" t="n"/>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
-          <t>강의 수호자</t>
+          <t>사제의 홀</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E49" s="20" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="I49" s="20" t="inlineStr">
         <is>
-          <t>강 하류(Lv3)</t>
+          <t>고대 신전(Lv3)</t>
         </is>
       </c>
       <c r="J49" s="11" t="n"/>
@@ -2362,12 +2362,12 @@
       </c>
       <c r="C50" s="20" t="inlineStr">
         <is>
-          <t>천년 쏘가리</t>
+          <t>신탁의 석판</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="I50" s="20" t="inlineStr">
         <is>
-          <t>강 하류(Lv3)</t>
+          <t>고대 신전(Lv3)</t>
         </is>
       </c>
       <c r="J50" s="11" t="n"/>
@@ -2398,12 +2398,12 @@
       </c>
       <c r="C51" s="20" t="inlineStr">
         <is>
-          <t>강신의 비늘</t>
+          <t>잊힌 신의 우상</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E51" s="20" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="I51" s="20" t="inlineStr">
         <is>
-          <t>강 하류(Lv3)</t>
+          <t>고대 신전(Lv3)</t>
         </is>
       </c>
       <c r="J51" s="11" t="n"/>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="C52" s="20" t="inlineStr">
         <is>
-          <t>빙어</t>
+          <t>오래된 뼈 조각</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="I52" s="20" t="inlineStr">
         <is>
-          <t>호수(Lv4)</t>
+          <t>지하 묘실(Lv4)</t>
         </is>
       </c>
       <c r="J52" s="11" t="n"/>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>송어</t>
+          <t>장신구 파편</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="I53" s="20" t="inlineStr">
         <is>
-          <t>호수(Lv4)</t>
+          <t>지하 묘실(Lv4)</t>
         </is>
       </c>
       <c r="J53" s="11" t="n"/>
@@ -2506,12 +2506,12 @@
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>무지개 송어</t>
+          <t>묘실 등잔</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="I54" s="20" t="inlineStr">
         <is>
-          <t>호수(Lv4)</t>
+          <t>지하 묘실(Lv4)</t>
         </is>
       </c>
       <c r="J54" s="11" t="n"/>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
-          <t>호수의 눈</t>
+          <t>황금 가면</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E55" s="20" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I55" s="20" t="inlineStr">
         <is>
-          <t>호수(Lv4)</t>
+          <t>지하 묘실(Lv4)</t>
         </is>
       </c>
       <c r="J55" s="11" t="n"/>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>심층 대어</t>
+          <t>왕비의 왕관</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="I56" s="20" t="inlineStr">
         <is>
-          <t>호수(Lv4)</t>
+          <t>지하 묘실(Lv4)</t>
         </is>
       </c>
       <c r="J56" s="11" t="n"/>
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>호수의 심장</t>
+          <t>불멸의 성배</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E57" s="20" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="I57" s="20" t="inlineStr">
         <is>
-          <t>호수(Lv4)</t>
+          <t>지하 묘실(Lv4)</t>
         </is>
       </c>
       <c r="J57" s="11" t="n"/>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>심해 새우</t>
+          <t>고대 주화</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="I58" s="20" t="inlineStr">
         <is>
-          <t>심해(Lv5)</t>
+          <t>잊힌 왕도(Lv5)</t>
         </is>
       </c>
       <c r="J58" s="11" t="n"/>
@@ -2686,12 +2686,12 @@
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>아귀</t>
+          <t>옥새 조각</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="I59" s="20" t="inlineStr">
         <is>
-          <t>심해(Lv5)</t>
+          <t>잊힌 왕도(Lv5)</t>
         </is>
       </c>
       <c r="J59" s="11" t="n"/>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>심해 등불고기</t>
+          <t>왕실 문서</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="I60" s="20" t="inlineStr">
         <is>
-          <t>심해(Lv5)</t>
+          <t>잊힌 왕도(Lv5)</t>
         </is>
       </c>
       <c r="J60" s="11" t="n"/>
@@ -2758,12 +2758,12 @@
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>대왕오징어</t>
+          <t>고대 왕의 홀</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E61" s="20" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="I61" s="20" t="inlineStr">
         <is>
-          <t>심해(Lv5)</t>
+          <t>잊힌 왕도(Lv5)</t>
         </is>
       </c>
       <c r="J61" s="11" t="n"/>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>해구의 지배자</t>
+          <t>왕도의 지도석</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="I62" s="20" t="inlineStr">
         <is>
-          <t>심해(Lv5)</t>
+          <t>잊힌 왕도(Lv5)</t>
         </is>
       </c>
       <c r="J62" s="11" t="n"/>
@@ -2830,12 +2830,12 @@
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>리바이어던의 조각</t>
+          <t>태초의 유물</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="E63" s="20" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="I63" s="20" t="inlineStr">
         <is>
-          <t>심해(Lv5)</t>
+          <t>잊힌 왕도(Lv5)</t>
         </is>
       </c>
       <c r="J63" s="11" t="n"/>

--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -6655,7 +6655,7 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Misc</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Misc</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Misc</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Misc</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Misc</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Misc</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Misc</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">

--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet name="ItemTable.자원" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ItemTable.Special" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ItemTable.유물" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -280,6 +281,26 @@
 </file>
 
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>레어도 (전역 등급)</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>기본 가격 (즉시 판매·거래소 하한의 기준)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>excel-table-creator</author>
@@ -600,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J159"/>
+  <dimension ref="A1:K159"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -613,6 +634,7 @@
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -626,6 +648,7 @@
       <c r="H1" s="11" t="n"/>
       <c r="I1" s="11" t="n"/>
       <c r="J1" s="11" t="n"/>
+      <c r="K1" s="11" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
@@ -678,6 +701,11 @@
           <t>툴팁</t>
         </is>
       </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>감정 비용</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -730,6 +758,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="K3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -780,6 +813,11 @@
       <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
@@ -802,6 +840,9 @@
       </c>
       <c r="I5" s="15" t="n"/>
       <c r="J5" s="15" t="n"/>
+      <c r="K5" s="15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -818,6 +859,7 @@
       <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="n"/>
+      <c r="K6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -846,6 +888,9 @@
           <t>""</t>
         </is>
       </c>
+      <c r="K7" s="15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -866,6 +911,7 @@
       </c>
       <c r="I8" s="15" t="n"/>
       <c r="J8" s="15" t="n"/>
+      <c r="K8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="n"/>
@@ -912,6 +958,11 @@
       <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Tooltip</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>OpenCostGold</t>
         </is>
       </c>
     </row>
@@ -950,6 +1001,9 @@
         </is>
       </c>
       <c r="J10" s="11" t="n"/>
+      <c r="K10" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n"/>
@@ -986,6 +1040,9 @@
         </is>
       </c>
       <c r="J11" s="11" t="n"/>
+      <c r="K11" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n"/>
@@ -1022,6 +1079,9 @@
         </is>
       </c>
       <c r="J12" s="11" t="n"/>
+      <c r="K12" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n"/>
@@ -1058,6 +1118,9 @@
         </is>
       </c>
       <c r="J13" s="11" t="n"/>
+      <c r="K13" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>
@@ -1094,6 +1157,9 @@
         </is>
       </c>
       <c r="J14" s="11" t="n"/>
+      <c r="K14" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="11" t="n"/>
@@ -1130,6 +1196,9 @@
         </is>
       </c>
       <c r="J15" s="11" t="n"/>
+      <c r="K15" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n"/>
@@ -1166,6 +1235,9 @@
         </is>
       </c>
       <c r="J16" s="11" t="n"/>
+      <c r="K16" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -1202,6 +1274,9 @@
         </is>
       </c>
       <c r="J17" s="11" t="n"/>
+      <c r="K17" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n"/>
@@ -1238,6 +1313,9 @@
         </is>
       </c>
       <c r="J18" s="11" t="n"/>
+      <c r="K18" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -1274,6 +1352,9 @@
         </is>
       </c>
       <c r="J19" s="11" t="n"/>
+      <c r="K19" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
@@ -1310,6 +1391,9 @@
         </is>
       </c>
       <c r="J20" s="11" t="n"/>
+      <c r="K20" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
@@ -1346,6 +1430,9 @@
         </is>
       </c>
       <c r="J21" s="11" t="n"/>
+      <c r="K21" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
@@ -1382,6 +1469,9 @@
         </is>
       </c>
       <c r="J22" s="11" t="n"/>
+      <c r="K22" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
@@ -1418,6 +1508,9 @@
         </is>
       </c>
       <c r="J23" s="11" t="n"/>
+      <c r="K23" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n"/>
@@ -1454,6 +1547,9 @@
         </is>
       </c>
       <c r="J24" s="11" t="n"/>
+      <c r="K24" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n"/>
@@ -1490,6 +1586,9 @@
         </is>
       </c>
       <c r="J25" s="11" t="n"/>
+      <c r="K25" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -1526,6 +1625,9 @@
         </is>
       </c>
       <c r="J26" s="11" t="n"/>
+      <c r="K26" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -1562,6 +1664,9 @@
         </is>
       </c>
       <c r="J27" s="11" t="n"/>
+      <c r="K27" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n"/>
@@ -1598,6 +1703,9 @@
         </is>
       </c>
       <c r="J28" s="11" t="n"/>
+      <c r="K28" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n"/>
@@ -1634,6 +1742,9 @@
         </is>
       </c>
       <c r="J29" s="11" t="n"/>
+      <c r="K29" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n"/>
@@ -1670,6 +1781,9 @@
         </is>
       </c>
       <c r="J30" s="11" t="n"/>
+      <c r="K30" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n"/>
@@ -1706,6 +1820,9 @@
         </is>
       </c>
       <c r="J31" s="11" t="n"/>
+      <c r="K31" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n"/>
@@ -1742,6 +1859,9 @@
         </is>
       </c>
       <c r="J32" s="11" t="n"/>
+      <c r="K32" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n"/>
@@ -1778,6 +1898,9 @@
         </is>
       </c>
       <c r="J33" s="11" t="n"/>
+      <c r="K33" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n"/>
@@ -1814,6 +1937,9 @@
         </is>
       </c>
       <c r="J34" s="11" t="n"/>
+      <c r="K34" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n"/>
@@ -1850,6 +1976,9 @@
         </is>
       </c>
       <c r="J35" s="11" t="n"/>
+      <c r="K35" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n"/>
@@ -1886,6 +2015,9 @@
         </is>
       </c>
       <c r="J36" s="11" t="n"/>
+      <c r="K36" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n"/>
@@ -1922,6 +2054,9 @@
         </is>
       </c>
       <c r="J37" s="11" t="n"/>
+      <c r="K37" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n"/>
@@ -1958,6 +2093,9 @@
         </is>
       </c>
       <c r="J38" s="11" t="n"/>
+      <c r="K38" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n"/>
@@ -1994,6 +2132,9 @@
         </is>
       </c>
       <c r="J39" s="11" t="n"/>
+      <c r="K39" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n"/>
@@ -2030,6 +2171,9 @@
         </is>
       </c>
       <c r="J40" s="11" t="n"/>
+      <c r="K40" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="n"/>
@@ -2066,6 +2210,9 @@
         </is>
       </c>
       <c r="J41" s="11" t="n"/>
+      <c r="K41" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="n"/>
@@ -2102,6 +2249,9 @@
         </is>
       </c>
       <c r="J42" s="11" t="n"/>
+      <c r="K42" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="n"/>
@@ -2138,6 +2288,9 @@
         </is>
       </c>
       <c r="J43" s="11" t="n"/>
+      <c r="K43" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="n"/>
@@ -2174,6 +2327,9 @@
         </is>
       </c>
       <c r="J44" s="11" t="n"/>
+      <c r="K44" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="n"/>
@@ -2210,6 +2366,9 @@
         </is>
       </c>
       <c r="J45" s="11" t="n"/>
+      <c r="K45" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="n"/>
@@ -2246,6 +2405,9 @@
         </is>
       </c>
       <c r="J46" s="11" t="n"/>
+      <c r="K46" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="n"/>
@@ -2282,6 +2444,9 @@
         </is>
       </c>
       <c r="J47" s="11" t="n"/>
+      <c r="K47" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="n"/>
@@ -2318,6 +2483,9 @@
         </is>
       </c>
       <c r="J48" s="11" t="n"/>
+      <c r="K48" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="n"/>
@@ -2354,6 +2522,9 @@
         </is>
       </c>
       <c r="J49" s="11" t="n"/>
+      <c r="K49" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="n"/>
@@ -2390,6 +2561,9 @@
         </is>
       </c>
       <c r="J50" s="11" t="n"/>
+      <c r="K50" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="n"/>
@@ -2426,6 +2600,9 @@
         </is>
       </c>
       <c r="J51" s="11" t="n"/>
+      <c r="K51" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n"/>
@@ -2462,6 +2639,9 @@
         </is>
       </c>
       <c r="J52" s="11" t="n"/>
+      <c r="K52" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n"/>
@@ -2498,6 +2678,9 @@
         </is>
       </c>
       <c r="J53" s="11" t="n"/>
+      <c r="K53" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n"/>
@@ -2534,6 +2717,9 @@
         </is>
       </c>
       <c r="J54" s="11" t="n"/>
+      <c r="K54" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="n"/>
@@ -2570,6 +2756,9 @@
         </is>
       </c>
       <c r="J55" s="11" t="n"/>
+      <c r="K55" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="n"/>
@@ -2606,6 +2795,9 @@
         </is>
       </c>
       <c r="J56" s="11" t="n"/>
+      <c r="K56" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="n"/>
@@ -2642,6 +2834,9 @@
         </is>
       </c>
       <c r="J57" s="11" t="n"/>
+      <c r="K57" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n"/>
@@ -2678,6 +2873,9 @@
         </is>
       </c>
       <c r="J58" s="11" t="n"/>
+      <c r="K58" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n"/>
@@ -2714,6 +2912,9 @@
         </is>
       </c>
       <c r="J59" s="11" t="n"/>
+      <c r="K59" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="n"/>
@@ -2750,6 +2951,9 @@
         </is>
       </c>
       <c r="J60" s="11" t="n"/>
+      <c r="K60" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n"/>
@@ -2786,6 +2990,9 @@
         </is>
       </c>
       <c r="J61" s="11" t="n"/>
+      <c r="K61" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n"/>
@@ -2822,6 +3029,9 @@
         </is>
       </c>
       <c r="J62" s="11" t="n"/>
+      <c r="K62" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="n"/>
@@ -2858,6 +3068,9 @@
         </is>
       </c>
       <c r="J63" s="11" t="n"/>
+      <c r="K63" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n"/>
@@ -2894,6 +3107,9 @@
         </is>
       </c>
       <c r="J64" s="11" t="n"/>
+      <c r="K64" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n"/>
@@ -2930,6 +3146,9 @@
         </is>
       </c>
       <c r="J65" s="11" t="n"/>
+      <c r="K65" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="n"/>
@@ -2966,6 +3185,9 @@
         </is>
       </c>
       <c r="J66" s="11" t="n"/>
+      <c r="K66" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n"/>
@@ -3002,6 +3224,9 @@
         </is>
       </c>
       <c r="J67" s="11" t="n"/>
+      <c r="K67" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n"/>
@@ -3038,6 +3263,9 @@
         </is>
       </c>
       <c r="J68" s="11" t="n"/>
+      <c r="K68" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n"/>
@@ -3074,6 +3302,9 @@
         </is>
       </c>
       <c r="J69" s="11" t="n"/>
+      <c r="K69" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="n"/>
@@ -3110,6 +3341,9 @@
         </is>
       </c>
       <c r="J70" s="11" t="n"/>
+      <c r="K70" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="n"/>
@@ -3146,6 +3380,9 @@
         </is>
       </c>
       <c r="J71" s="11" t="n"/>
+      <c r="K71" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="n"/>
@@ -3182,6 +3419,9 @@
         </is>
       </c>
       <c r="J72" s="11" t="n"/>
+      <c r="K72" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n"/>
@@ -3218,6 +3458,9 @@
         </is>
       </c>
       <c r="J73" s="11" t="n"/>
+      <c r="K73" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="n"/>
@@ -3254,6 +3497,9 @@
         </is>
       </c>
       <c r="J74" s="11" t="n"/>
+      <c r="K74" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n"/>
@@ -3290,6 +3536,9 @@
         </is>
       </c>
       <c r="J75" s="11" t="n"/>
+      <c r="K75" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n"/>
@@ -3326,6 +3575,9 @@
         </is>
       </c>
       <c r="J76" s="11" t="n"/>
+      <c r="K76" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n"/>
@@ -3362,6 +3614,9 @@
         </is>
       </c>
       <c r="J77" s="11" t="n"/>
+      <c r="K77" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n"/>
@@ -3398,6 +3653,9 @@
         </is>
       </c>
       <c r="J78" s="11" t="n"/>
+      <c r="K78" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="n"/>
@@ -3434,6 +3692,9 @@
         </is>
       </c>
       <c r="J79" s="11" t="n"/>
+      <c r="K79" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n"/>
@@ -3470,6 +3731,9 @@
         </is>
       </c>
       <c r="J80" s="11" t="n"/>
+      <c r="K80" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="n"/>
@@ -3506,6 +3770,9 @@
         </is>
       </c>
       <c r="J81" s="11" t="n"/>
+      <c r="K81" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="n"/>
@@ -3542,6 +3809,9 @@
         </is>
       </c>
       <c r="J82" s="11" t="n"/>
+      <c r="K82" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="n"/>
@@ -3578,6 +3848,9 @@
         </is>
       </c>
       <c r="J83" s="11" t="n"/>
+      <c r="K83" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="n"/>
@@ -3614,6 +3887,9 @@
         </is>
       </c>
       <c r="J84" s="11" t="n"/>
+      <c r="K84" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="n"/>
@@ -3650,6 +3926,9 @@
         </is>
       </c>
       <c r="J85" s="11" t="n"/>
+      <c r="K85" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="n"/>
@@ -3686,6 +3965,9 @@
         </is>
       </c>
       <c r="J86" s="11" t="n"/>
+      <c r="K86" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="n"/>
@@ -3722,6 +4004,9 @@
         </is>
       </c>
       <c r="J87" s="11" t="n"/>
+      <c r="K87" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="n"/>
@@ -3758,6 +4043,9 @@
         </is>
       </c>
       <c r="J88" s="11" t="n"/>
+      <c r="K88" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n"/>
@@ -3794,6 +4082,9 @@
         </is>
       </c>
       <c r="J89" s="11" t="n"/>
+      <c r="K89" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n"/>
@@ -3830,6 +4121,9 @@
         </is>
       </c>
       <c r="J90" s="11" t="n"/>
+      <c r="K90" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="n"/>
@@ -3866,6 +4160,9 @@
         </is>
       </c>
       <c r="J91" s="11" t="n"/>
+      <c r="K91" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="n"/>
@@ -3902,6 +4199,9 @@
         </is>
       </c>
       <c r="J92" s="11" t="n"/>
+      <c r="K92" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="n"/>
@@ -3938,6 +4238,9 @@
         </is>
       </c>
       <c r="J93" s="11" t="n"/>
+      <c r="K93" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="n"/>
@@ -3974,6 +4277,9 @@
         </is>
       </c>
       <c r="J94" s="11" t="n"/>
+      <c r="K94" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="n"/>
@@ -4010,6 +4316,9 @@
         </is>
       </c>
       <c r="J95" s="11" t="n"/>
+      <c r="K95" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="n"/>
@@ -4046,6 +4355,9 @@
         </is>
       </c>
       <c r="J96" s="11" t="n"/>
+      <c r="K96" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="n"/>
@@ -4082,6 +4394,9 @@
         </is>
       </c>
       <c r="J97" s="11" t="n"/>
+      <c r="K97" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="n"/>
@@ -4118,6 +4433,9 @@
         </is>
       </c>
       <c r="J98" s="11" t="n"/>
+      <c r="K98" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="n"/>
@@ -4154,6 +4472,9 @@
         </is>
       </c>
       <c r="J99" s="11" t="n"/>
+      <c r="K99" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="n"/>
@@ -4190,6 +4511,9 @@
         </is>
       </c>
       <c r="J100" s="11" t="n"/>
+      <c r="K100" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="n"/>
@@ -4226,6 +4550,9 @@
         </is>
       </c>
       <c r="J101" s="11" t="n"/>
+      <c r="K101" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="n"/>
@@ -4262,6 +4589,9 @@
         </is>
       </c>
       <c r="J102" s="11" t="n"/>
+      <c r="K102" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="n"/>
@@ -4298,6 +4628,9 @@
         </is>
       </c>
       <c r="J103" s="11" t="n"/>
+      <c r="K103" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="n"/>
@@ -4334,6 +4667,9 @@
         </is>
       </c>
       <c r="J104" s="11" t="n"/>
+      <c r="K104" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="n"/>
@@ -4370,6 +4706,9 @@
         </is>
       </c>
       <c r="J105" s="11" t="n"/>
+      <c r="K105" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="n"/>
@@ -4406,6 +4745,9 @@
         </is>
       </c>
       <c r="J106" s="11" t="n"/>
+      <c r="K106" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="n"/>
@@ -4442,6 +4784,9 @@
         </is>
       </c>
       <c r="J107" s="11" t="n"/>
+      <c r="K107" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="n"/>
@@ -4478,6 +4823,9 @@
         </is>
       </c>
       <c r="J108" s="11" t="n"/>
+      <c r="K108" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="11" t="n"/>
@@ -4514,6 +4862,9 @@
         </is>
       </c>
       <c r="J109" s="11" t="n"/>
+      <c r="K109" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="11" t="n"/>
@@ -4550,6 +4901,9 @@
         </is>
       </c>
       <c r="J110" s="11" t="n"/>
+      <c r="K110" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="n"/>
@@ -4586,6 +4940,9 @@
         </is>
       </c>
       <c r="J111" s="11" t="n"/>
+      <c r="K111" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="n"/>
@@ -4622,6 +4979,9 @@
         </is>
       </c>
       <c r="J112" s="11" t="n"/>
+      <c r="K112" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="n"/>
@@ -4658,6 +5018,9 @@
         </is>
       </c>
       <c r="J113" s="11" t="n"/>
+      <c r="K113" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="n"/>
@@ -4694,6 +5057,9 @@
         </is>
       </c>
       <c r="J114" s="11" t="n"/>
+      <c r="K114" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="n"/>
@@ -4730,6 +5096,9 @@
         </is>
       </c>
       <c r="J115" s="11" t="n"/>
+      <c r="K115" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="n"/>
@@ -4766,6 +5135,9 @@
         </is>
       </c>
       <c r="J116" s="11" t="n"/>
+      <c r="K116" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="n"/>
@@ -4802,6 +5174,9 @@
         </is>
       </c>
       <c r="J117" s="11" t="n"/>
+      <c r="K117" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="n"/>
@@ -4838,6 +5213,9 @@
         </is>
       </c>
       <c r="J118" s="11" t="n"/>
+      <c r="K118" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="n"/>
@@ -4874,6 +5252,9 @@
         </is>
       </c>
       <c r="J119" s="11" t="n"/>
+      <c r="K119" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="11" t="n"/>
@@ -4910,6 +5291,9 @@
         </is>
       </c>
       <c r="J120" s="11" t="n"/>
+      <c r="K120" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="n"/>
@@ -4946,6 +5330,9 @@
         </is>
       </c>
       <c r="J121" s="11" t="n"/>
+      <c r="K121" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="11" t="n"/>
@@ -4982,6 +5369,9 @@
         </is>
       </c>
       <c r="J122" s="11" t="n"/>
+      <c r="K122" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="n"/>
@@ -5018,6 +5408,9 @@
         </is>
       </c>
       <c r="J123" s="11" t="n"/>
+      <c r="K123" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="11" t="n"/>
@@ -5054,6 +5447,9 @@
         </is>
       </c>
       <c r="J124" s="11" t="n"/>
+      <c r="K124" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="n"/>
@@ -5090,6 +5486,9 @@
         </is>
       </c>
       <c r="J125" s="11" t="n"/>
+      <c r="K125" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="11" t="n"/>
@@ -5126,6 +5525,9 @@
         </is>
       </c>
       <c r="J126" s="11" t="n"/>
+      <c r="K126" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="n"/>
@@ -5162,6 +5564,9 @@
         </is>
       </c>
       <c r="J127" s="11" t="n"/>
+      <c r="K127" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="n"/>
@@ -5198,6 +5603,9 @@
         </is>
       </c>
       <c r="J128" s="11" t="n"/>
+      <c r="K128" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="n"/>
@@ -5234,6 +5642,9 @@
         </is>
       </c>
       <c r="J129" s="11" t="n"/>
+      <c r="K129" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="n"/>
@@ -5270,6 +5681,9 @@
         </is>
       </c>
       <c r="J130" s="11" t="n"/>
+      <c r="K130" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="11" t="n"/>
@@ -5306,6 +5720,9 @@
         </is>
       </c>
       <c r="J131" s="11" t="n"/>
+      <c r="K131" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="11" t="n"/>
@@ -5342,6 +5759,9 @@
         </is>
       </c>
       <c r="J132" s="11" t="n"/>
+      <c r="K132" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="11" t="n"/>
@@ -5378,6 +5798,9 @@
         </is>
       </c>
       <c r="J133" s="11" t="n"/>
+      <c r="K133" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="n"/>
@@ -5414,6 +5837,9 @@
         </is>
       </c>
       <c r="J134" s="11" t="n"/>
+      <c r="K134" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="11" t="n"/>
@@ -5450,6 +5876,9 @@
         </is>
       </c>
       <c r="J135" s="11" t="n"/>
+      <c r="K135" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="11" t="n"/>
@@ -5486,6 +5915,9 @@
         </is>
       </c>
       <c r="J136" s="11" t="n"/>
+      <c r="K136" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="n"/>
@@ -5522,6 +5954,9 @@
         </is>
       </c>
       <c r="J137" s="11" t="n"/>
+      <c r="K137" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="11" t="n"/>
@@ -5558,6 +5993,9 @@
         </is>
       </c>
       <c r="J138" s="11" t="n"/>
+      <c r="K138" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="11" t="n"/>
@@ -5594,6 +6032,9 @@
         </is>
       </c>
       <c r="J139" s="11" t="n"/>
+      <c r="K139" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="11" t="n"/>
@@ -5630,6 +6071,9 @@
         </is>
       </c>
       <c r="J140" s="11" t="n"/>
+      <c r="K140" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="11" t="n"/>
@@ -5666,6 +6110,9 @@
         </is>
       </c>
       <c r="J141" s="11" t="n"/>
+      <c r="K141" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="11" t="n"/>
@@ -5702,6 +6149,9 @@
         </is>
       </c>
       <c r="J142" s="11" t="n"/>
+      <c r="K142" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="11" t="n"/>
@@ -5738,6 +6188,9 @@
         </is>
       </c>
       <c r="J143" s="11" t="n"/>
+      <c r="K143" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="11" t="n"/>
@@ -5774,6 +6227,9 @@
         </is>
       </c>
       <c r="J144" s="11" t="n"/>
+      <c r="K144" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="n"/>
@@ -5810,6 +6266,9 @@
         </is>
       </c>
       <c r="J145" s="11" t="n"/>
+      <c r="K145" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="11" t="n"/>
@@ -5846,6 +6305,9 @@
         </is>
       </c>
       <c r="J146" s="11" t="n"/>
+      <c r="K146" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="11" t="n"/>
@@ -5882,6 +6344,9 @@
         </is>
       </c>
       <c r="J147" s="11" t="n"/>
+      <c r="K147" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="11" t="n"/>
@@ -5918,6 +6383,9 @@
         </is>
       </c>
       <c r="J148" s="11" t="n"/>
+      <c r="K148" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="11" t="n"/>
@@ -5954,6 +6422,9 @@
         </is>
       </c>
       <c r="J149" s="11" t="n"/>
+      <c r="K149" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="11" t="n"/>
@@ -5990,6 +6461,9 @@
         </is>
       </c>
       <c r="J150" s="11" t="n"/>
+      <c r="K150" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="11" t="n"/>
@@ -6026,6 +6500,9 @@
         </is>
       </c>
       <c r="J151" s="11" t="n"/>
+      <c r="K151" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="11" t="n"/>
@@ -6062,6 +6539,9 @@
         </is>
       </c>
       <c r="J152" s="11" t="n"/>
+      <c r="K152" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="11" t="n"/>
@@ -6098,6 +6578,9 @@
         </is>
       </c>
       <c r="J153" s="11" t="n"/>
+      <c r="K153" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="11" t="n"/>
@@ -6134,6 +6617,9 @@
         </is>
       </c>
       <c r="J154" s="11" t="n"/>
+      <c r="K154" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="11" t="n"/>
@@ -6170,6 +6656,9 @@
         </is>
       </c>
       <c r="J155" s="11" t="n"/>
+      <c r="K155" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="11" t="n"/>
@@ -6206,6 +6695,9 @@
         </is>
       </c>
       <c r="J156" s="11" t="n"/>
+      <c r="K156" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="11" t="n"/>
@@ -6242,6 +6734,9 @@
         </is>
       </c>
       <c r="J157" s="11" t="n"/>
+      <c r="K157" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="11" t="n"/>
@@ -6278,6 +6773,9 @@
         </is>
       </c>
       <c r="J158" s="11" t="n"/>
+      <c r="K158" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="11" t="n"/>
@@ -6314,6 +6812,9 @@
         </is>
       </c>
       <c r="J159" s="11" t="n"/>
+      <c r="K159" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6328,7 +6829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6341,6 +6842,7 @@
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6354,6 +6856,7 @@
       <c r="H1" s="11" t="n"/>
       <c r="I1" s="11" t="n"/>
       <c r="J1" s="11" t="n"/>
+      <c r="K1" s="11" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
@@ -6406,6 +6909,11 @@
           <t>툴팁</t>
         </is>
       </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>감정 비용</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -6458,6 +6966,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="K3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -6508,6 +7021,11 @@
       <c r="J4" s="15" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
@@ -6530,6 +7048,9 @@
       </c>
       <c r="I5" s="15" t="n"/>
       <c r="J5" s="15" t="n"/>
+      <c r="K5" s="15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -6546,6 +7067,7 @@
       <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="n"/>
+      <c r="K6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -6574,6 +7096,9 @@
           <t>""</t>
         </is>
       </c>
+      <c r="K7" s="15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -6594,6 +7119,7 @@
       </c>
       <c r="I8" s="15" t="n"/>
       <c r="J8" s="15" t="n"/>
+      <c r="K8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="n"/>
@@ -6640,6 +7166,11 @@
       <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Tooltip</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>OpenCostGold</t>
         </is>
       </c>
     </row>
@@ -6678,6 +7209,9 @@
         </is>
       </c>
       <c r="J10" s="11" t="n"/>
+      <c r="K10" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n"/>
@@ -6714,6 +7248,9 @@
         </is>
       </c>
       <c r="J11" s="11" t="n"/>
+      <c r="K11" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n"/>
@@ -6750,6 +7287,9 @@
         </is>
       </c>
       <c r="J12" s="11" t="n"/>
+      <c r="K12" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n"/>
@@ -6786,6 +7326,9 @@
         </is>
       </c>
       <c r="J13" s="11" t="n"/>
+      <c r="K13" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>
@@ -6822,6 +7365,9 @@
         </is>
       </c>
       <c r="J14" s="11" t="n"/>
+      <c r="K14" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="11" t="n"/>
@@ -6858,6 +7404,9 @@
         </is>
       </c>
       <c r="J15" s="11" t="n"/>
+      <c r="K15" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n"/>
@@ -6894,6 +7443,9 @@
         </is>
       </c>
       <c r="J16" s="11" t="n"/>
+      <c r="K16" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -6930,6 +7482,9 @@
         </is>
       </c>
       <c r="J17" s="11" t="n"/>
+      <c r="K17" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n"/>
@@ -6966,6 +7521,9 @@
         </is>
       </c>
       <c r="J18" s="11" t="n"/>
+      <c r="K18" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -7002,6 +7560,9 @@
         </is>
       </c>
       <c r="J19" s="11" t="n"/>
+      <c r="K19" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
@@ -7038,6 +7599,9 @@
         </is>
       </c>
       <c r="J20" s="11" t="n"/>
+      <c r="K20" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
@@ -7074,6 +7638,9 @@
         </is>
       </c>
       <c r="J21" s="11" t="n"/>
+      <c r="K21" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
@@ -7110,6 +7677,9 @@
         </is>
       </c>
       <c r="J22" s="11" t="n"/>
+      <c r="K22" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
@@ -7146,6 +7716,9 @@
         </is>
       </c>
       <c r="J23" s="11" t="n"/>
+      <c r="K23" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n"/>
@@ -7182,6 +7755,9 @@
         </is>
       </c>
       <c r="J24" s="11" t="n"/>
+      <c r="K24" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n"/>
@@ -7218,6 +7794,9 @@
         </is>
       </c>
       <c r="J25" s="11" t="n"/>
+      <c r="K25" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -7254,6 +7833,9 @@
         </is>
       </c>
       <c r="J26" s="11" t="n"/>
+      <c r="K26" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -7290,6 +7872,9 @@
         </is>
       </c>
       <c r="J27" s="11" t="n"/>
+      <c r="K27" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n"/>
@@ -7326,6 +7911,9 @@
         </is>
       </c>
       <c r="J28" s="11" t="n"/>
+      <c r="K28" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n"/>
@@ -7362,6 +7950,9 @@
         </is>
       </c>
       <c r="J29" s="11" t="n"/>
+      <c r="K29" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n"/>
@@ -7398,6 +7989,9 @@
         </is>
       </c>
       <c r="J30" s="11" t="n"/>
+      <c r="K30" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n"/>
@@ -7434,6 +8028,9 @@
         </is>
       </c>
       <c r="J31" s="11" t="n"/>
+      <c r="K31" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n"/>
@@ -7470,6 +8067,9 @@
         </is>
       </c>
       <c r="J32" s="11" t="n"/>
+      <c r="K32" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n"/>
@@ -7506,6 +8106,9 @@
         </is>
       </c>
       <c r="J33" s="11" t="n"/>
+      <c r="K33" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n"/>
@@ -7542,6 +8145,9 @@
         </is>
       </c>
       <c r="J34" s="11" t="n"/>
+      <c r="K34" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n"/>
@@ -7578,6 +8184,9 @@
         </is>
       </c>
       <c r="J35" s="11" t="n"/>
+      <c r="K35" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n"/>
@@ -7614,6 +8223,9 @@
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr"/>
+      <c r="K36" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n"/>
@@ -7650,6 +8262,9 @@
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr"/>
+      <c r="K37" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n"/>
@@ -7686,6 +8301,9 @@
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr"/>
+      <c r="K38" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n"/>
@@ -7722,6 +8340,9 @@
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr"/>
+      <c r="K39" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n"/>
@@ -7758,6 +8379,9 @@
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr"/>
+      <c r="K40" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="n"/>
@@ -7794,6 +8418,9 @@
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr"/>
+      <c r="K41" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="n"/>
@@ -7830,6 +8457,668 @@
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr"/>
+      <c r="K42" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="59" customWidth="1" min="9" max="9"/>
+    <col width="51" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="n"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+      <c r="G1" s="11" t="n"/>
+      <c r="H1" s="11" t="n"/>
+      <c r="I1" s="11" t="n"/>
+      <c r="J1" s="11" t="n"/>
+      <c r="K1" s="11" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>아이템 TID</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>아이템 타입</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>레어도</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>최대 수량</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>기본 가격</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>여는 풀</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>툴팁</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>감정 비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="K3" s="15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>eItemType</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>eGlobalRarity</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
+      <c r="K5" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
+      <c r="K6" s="15" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>GachaInfoTable.GachaInfoTID?</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
+      <c r="K8" s="15" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>ItemTID</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>ItemType</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>GlobalRarity</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>MaxStack</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>BasePrice</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>OpenGachaId</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>Tooltip</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>OpenCostGold</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="19" t="n">
+        <v>100061</v>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>흙 묻은 유물</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>일반 미감정 유물 · 감정 200골드 (테스트값 — T-150)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+        </is>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="19" t="n">
+        <v>100062</v>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>조개 박힌 유물</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>고급 미감정 유물 · 감정 600골드 (테스트값 — T-150)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+        </is>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="19" t="n">
+        <v>100063</v>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>산호 엉긴 유물</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>900</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>희귀 미감정 유물 · 감정 1,800골드 (테스트값 — T-150)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="19" t="n">
+        <v>100064</v>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>봉인된 유물</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>2700</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>영웅 미감정 유물 · 감정 5,400골드 (테스트값 — T-150)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+        </is>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="19" t="n">
+        <v>100065</v>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>황금 띠 유물</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>전설 미감정 유물 · 감정 16,000골드 (테스트값 — T-150)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+        </is>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customHeight="1">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="19" t="n">
+        <v>100066</v>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>왕의 유물</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>24000</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>신화 미감정 유물 · 감정 48,000골드 (테스트값 — T-150)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+        </is>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="19" t="n">
+        <v>100067</v>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>무지개 유물</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>75000</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>31</v>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>Special 미감정 유물 · 감정 150,000골드 (테스트값 — T-150)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>골드 {OpenCostGold}을 내고 감정하면 무언가 나온다</t>
+        </is>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>150000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -616,7 +616,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -629,7 +629,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="7"/>
+    <col width="16" customWidth="1" min="6" max="7"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>최대 수량</t>
+          <t>칸당 최대 수량</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
@@ -6819,12 +6819,12 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -6837,7 +6837,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="7"/>
+    <col width="16" customWidth="1" min="6" max="7"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>최대 수량</t>
+          <t>칸당 최대 수량</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
@@ -8464,12 +8464,12 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -8482,7 +8482,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="7"/>
+    <col width="16" customWidth="1" min="6" max="7"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="59" customWidth="1" min="9" max="9"/>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>최대 수량</t>
+          <t>칸당 최대 수량</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
@@ -9123,6 +9123,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -777,42 +777,42 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
+          <t>lstring</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>eItemType</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>eGlobalRarity</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>eItemType</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>eGlobalRarity</t>
-        </is>
-      </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="J4" s="15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="K4" s="15" t="inlineStr">
@@ -6985,42 +6985,42 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
+          <t>lstring</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>eItemType</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>eGlobalRarity</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>eItemType</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>eGlobalRarity</t>
-        </is>
-      </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="J4" s="15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="K4" s="15" t="inlineStr">
@@ -8630,42 +8630,42 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
+          <t>lstring</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>eItemType</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>eGlobalRarity</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>eItemType</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>eGlobalRarity</t>
-        </is>
-      </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H4" s="15" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="J4" s="15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="K4" s="15" t="inlineStr">

--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -616,7 +616,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -629,7 +629,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -6819,12 +6819,12 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -6837,7 +6837,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>마력의 파편</t>
+          <t>마석</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -8464,12 +8464,12 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -8482,7 +8482,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="59" customWidth="1" min="9" max="9"/>
@@ -9123,6 +9123,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Item.xlsx
+++ b/GameDesign/Excel/Item.xlsx
@@ -6829,7 +6829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6841,7 +6841,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -8458,6 +8458,178 @@
       </c>
       <c r="J42" s="11" t="inlineStr"/>
       <c r="K42" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="19" t="n">
+        <v>100071</v>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>캐릭터 뽑기권 A</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G43" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="I43" s="20" t="inlineStr">
+        <is>
+          <t>골드 상점 품목(가격은 ShopTable) · 희귀 이하 캐릭터 1명 (#78)</t>
+        </is>
+      </c>
+      <c r="J43" s="20" t="inlineStr">
+        <is>
+          <t>열면 희귀 이하 캐릭터 1명이 나온다</t>
+        </is>
+      </c>
+      <c r="K43" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="19" t="n">
+        <v>100072</v>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>캐릭터 뽑기권 B</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F44" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G44" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H44" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="I44" s="20" t="inlineStr">
+        <is>
+          <t>골드 상점 품목(가격은 ShopTable) · 영웅 이하 캐릭터 1명 (#78)</t>
+        </is>
+      </c>
+      <c r="J44" s="20" t="inlineStr">
+        <is>
+          <t>열면 영웅 이하 캐릭터 1명이 나온다</t>
+        </is>
+      </c>
+      <c r="K44" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="n"/>
+      <c r="B45" s="19" t="n">
+        <v>100073</v>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>캐릭터 뽑기권 C</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G45" s="19" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="I45" s="20" t="inlineStr">
+        <is>
+          <t>골드 상점 품목(가격은 ShopTable) · 전설 이하 캐릭터 1명 (#78)</t>
+        </is>
+      </c>
+      <c r="J45" s="20" t="inlineStr">
+        <is>
+          <t>열면 전설 이하 캐릭터 1명이 나온다</t>
+        </is>
+      </c>
+      <c r="K45" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="n"/>
+      <c r="B46" s="19" t="n">
+        <v>100074</v>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>캐릭터 뽑기권 D</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F46" s="19" t="n">
+        <v>9999</v>
+      </c>
+      <c r="G46" s="19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>35</v>
+      </c>
+      <c r="I46" s="20" t="inlineStr">
+        <is>
+          <t>골드 상점 품목(가격은 ShopTable) · 신화 이하 캐릭터 1명 (#78)</t>
+        </is>
+      </c>
+      <c r="J46" s="20" t="inlineStr">
+        <is>
+          <t>열면 신화 이하 캐릭터 1명이 나온다</t>
+        </is>
+      </c>
+      <c r="K46" s="19" t="n">
         <v>0</v>
       </c>
     </row>
